--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BD865BC-507A-4933-9699-2614343CDC2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA53357-E093-4CAD-BC0F-8C874FF4E08F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD02A4E5-99C3-4575-B1F2-C3DA70706224}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6397077E-A5C2-4B2B-A8DE-B739114D2057}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1A08C7E-117B-47F2-9F77-1BBF24FC41F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C447155-E6E1-45EF-BE93-AE3A2A9D0362}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA53357-E093-4CAD-BC0F-8C874FF4E08F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3727DA9B-C1F1-4F64-96B3-6B3B2828ADD2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6397077E-A5C2-4B2B-A8DE-B739114D2057}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78FF56C9-A0F0-408B-AF53-AB4E754EADE7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C447155-E6E1-45EF-BE93-AE3A2A9D0362}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2D6CAC6-384F-4124-87B8-883CA4CFD071}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3727DA9B-C1F1-4F64-96B3-6B3B2828ADD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91337087-26EC-4735-A43E-45A6392C73E5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78FF56C9-A0F0-408B-AF53-AB4E754EADE7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32124642-24E0-4B50-AA28-F8604A8E5B72}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2D6CAC6-384F-4124-87B8-883CA4CFD071}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69A330CE-0A18-4C0B-925F-92BCA452D8B0}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9887,13 +9887,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91337087-26EC-4735-A43E-45A6392C73E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD278CA0-F517-4389-9898-351629961DB5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32124642-24E0-4B50-AA28-F8604A8E5B72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4BD0F19-144F-4FB9-9E7A-3A0BCF9A09F0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69A330CE-0A18-4C0B-925F-92BCA452D8B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{189146BE-7A7B-461E-AA14-CE97262A31DA}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -11,6 +11,641 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="210">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Body_weight</t>
+  </si>
+  <si>
+    <t>Brain_weight_g</t>
+  </si>
+  <si>
+    <t>Neonate_brain_weight_g</t>
+  </si>
+  <si>
+    <t>Neocortex_mm^3</t>
+  </si>
+  <si>
+    <t>GI</t>
+  </si>
+  <si>
+    <t>Ventricle_mm^3</t>
+  </si>
+  <si>
+    <t>Maximum_lifespan_yrs</t>
+  </si>
+  <si>
+    <t>Age_at_first_breeding_F_mnths</t>
+  </si>
+  <si>
+    <t>Age_at_first_breeding_days</t>
+  </si>
+  <si>
+    <t>Female_sexual_maturity_days</t>
+  </si>
+  <si>
+    <t>Male_sexual_maturity_days</t>
+  </si>
+  <si>
+    <t>Gestation_days</t>
+  </si>
+  <si>
+    <t>Litter_size</t>
+  </si>
+  <si>
+    <t>Litters_per_year</t>
+  </si>
+  <si>
+    <t>Inter-litter_interval_days</t>
+  </si>
+  <si>
+    <t>Weaning_period_days</t>
+  </si>
+  <si>
+    <t>Weight_at_birth_g</t>
+  </si>
+  <si>
+    <t>Weight_at_weaning_g</t>
+  </si>
+  <si>
+    <t>Juvenility_primates_years</t>
+  </si>
+  <si>
+    <t>Juvenility_days</t>
+  </si>
+  <si>
+    <t>Max_home_range_ha</t>
+  </si>
+  <si>
+    <t>% Fruit and seeds</t>
+  </si>
+  <si>
+    <t>Activity_timing</t>
+  </si>
+  <si>
+    <t>Diet_breadth</t>
+  </si>
+  <si>
+    <t>Trophic_level</t>
+  </si>
+  <si>
+    <t>Population_group_size</t>
+  </si>
+  <si>
+    <t>Social_group_size</t>
+  </si>
+  <si>
+    <t>Adult_head_body_length_mm</t>
+  </si>
+  <si>
+    <t>Age_at_eye_opening_days</t>
+  </si>
+  <si>
+    <t>Altricial_precocial</t>
+  </si>
+  <si>
+    <t>Basal_metabolic_rate</t>
+  </si>
+  <si>
+    <t>Dispersal_age_days</t>
+  </si>
+  <si>
+    <t>Habitat_breadth</t>
+  </si>
+  <si>
+    <t>Social_system</t>
+  </si>
+  <si>
+    <t>Glia_neuron_ratio</t>
+  </si>
+  <si>
+    <t>Neuronal_density</t>
+  </si>
+  <si>
+    <t>Glial_cell_density</t>
+  </si>
+  <si>
+    <t>Neurogenic_period_days</t>
+  </si>
+  <si>
+    <t>Phylo_rank</t>
+  </si>
+  <si>
+    <t>Tachyglossus_aculeatus</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Mus musculus</t>
+  </si>
+  <si>
+    <t>Mus_musculus</t>
+  </si>
+  <si>
+    <t>Rattus norvegicus</t>
+  </si>
+  <si>
+    <t>Rattus_norvegicus</t>
+  </si>
+  <si>
+    <t>Mesocricetus_auratus</t>
+  </si>
+  <si>
+    <t>Castor_canadensis</t>
+  </si>
+  <si>
+    <t>5.0999999999999996</t>
+  </si>
+  <si>
+    <t>Hydrochoerus_hydrochaeris</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Dasyprocta_leporina</t>
+  </si>
+  <si>
+    <t>Oryctolagus cuniculus</t>
+  </si>
+  <si>
+    <t>Oryctolagus_cuniculus*</t>
+  </si>
+  <si>
+    <t>Cercopithecus_mitis</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Erythrocebus_patas</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Miopithecus_talapoin</t>
+  </si>
+  <si>
+    <t>91.2</t>
+  </si>
+  <si>
+    <t>Mandrillus_sphinx*</t>
+  </si>
+  <si>
+    <t>13.9</t>
+  </si>
+  <si>
+    <t>Lophocebus_albigena</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Papio_hamadryas</t>
+  </si>
+  <si>
+    <t>36.9</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Macaca_mulatta</t>
+  </si>
+  <si>
+    <t>38.5</t>
+  </si>
+  <si>
+    <t>Piliocolobus_badius</t>
+  </si>
+  <si>
+    <t>&gt;10</t>
+  </si>
+  <si>
+    <t>Pygathrix_nemaeus</t>
+  </si>
+  <si>
+    <t>9.3000000000000007</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Gorilla_gorilla</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Homo_sapiens</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Pan_troglodytes</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Pongo_pygmaeus</t>
+  </si>
+  <si>
+    <t>Hylobates_lar</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Alouatta_palliata*</t>
+  </si>
+  <si>
+    <t>13.1</t>
+  </si>
+  <si>
+    <t>Alouatta_seniculus</t>
+  </si>
+  <si>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>Ateles_paniscus</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Lagothrix_lagothricha</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Callicebus_moloch*</t>
+  </si>
+  <si>
+    <t>2.95</t>
+  </si>
+  <si>
+    <t>Aotus nancymaae</t>
+  </si>
+  <si>
+    <t>Aotus_trivirgatus</t>
+  </si>
+  <si>
+    <t>3.15</t>
+  </si>
+  <si>
+    <t>Callimico_goeldii</t>
+  </si>
+  <si>
+    <t>6.85</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Callithrix_jacchus</t>
+  </si>
+  <si>
+    <t>8.5500000000000007</t>
+  </si>
+  <si>
+    <t>Saguinus_midas</t>
+  </si>
+  <si>
+    <t>5.55</t>
+  </si>
+  <si>
+    <t>Saguinus_oedipus</t>
+  </si>
+  <si>
+    <t>7.05</t>
+  </si>
+  <si>
+    <t>Cebus_albifrons</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Saimiri boliviensis boliviensis</t>
+  </si>
+  <si>
+    <t>Saimiri_sciureus</t>
+  </si>
+  <si>
+    <t>36.090000000000003</t>
+  </si>
+  <si>
+    <t>Tarsius_bancanus</t>
+  </si>
+  <si>
+    <t>Tarsius_syrichta</t>
+  </si>
+  <si>
+    <t>Microcebus murinus</t>
+  </si>
+  <si>
+    <t>Microcebus_murinus</t>
+  </si>
+  <si>
+    <t>Cheirogaleus_major</t>
+  </si>
+  <si>
+    <t>Cheirogaleus_medius</t>
+  </si>
+  <si>
+    <t>Avahi_laniger</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Avahi_occidentalis</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Propithecus_verreauxi</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>Indri_indri</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Daubentonia_madagascariensis</t>
+  </si>
+  <si>
+    <t>Eulemur_fulvus</t>
+  </si>
+  <si>
+    <t>9.15</t>
+  </si>
+  <si>
+    <t>Eulemur_mongoz</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>Lemur_catta</t>
+  </si>
+  <si>
+    <t>16.45</t>
+  </si>
+  <si>
+    <t>Varecia_variegata</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>Lepilemur_ruficaudatus</t>
+  </si>
+  <si>
+    <t>Perodicticus_potto</t>
+  </si>
+  <si>
+    <t>Loris_tardigradus</t>
+  </si>
+  <si>
+    <t>Nycticebus_coucang</t>
+  </si>
+  <si>
+    <t>Galago_senegalensis</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Otolemur garnettii</t>
+  </si>
+  <si>
+    <t>Otolemur_crassicaudatus</t>
+  </si>
+  <si>
+    <t>Galago_demidoff</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>Cynocephalus_volans*</t>
+  </si>
+  <si>
+    <t>Tupaia belangeri</t>
+  </si>
+  <si>
+    <t>Tupaia_glis*</t>
+  </si>
+  <si>
+    <t>Ovis_aries</t>
+  </si>
+  <si>
+    <t>Capra_hircus_domestica*</t>
+  </si>
+  <si>
+    <t>Bos_taurus_indicus</t>
+  </si>
+  <si>
+    <t>Odocoileus_virginiatus</t>
+  </si>
+  <si>
+    <t>2.25</t>
+  </si>
+  <si>
+    <t>Phocoena_phocoena</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Delphinus_delphis</t>
+  </si>
+  <si>
+    <t>Tursiops_truncatus</t>
+  </si>
+  <si>
+    <t>Pseudorca_crassidens</t>
+  </si>
+  <si>
+    <t>Globicephala_macrorhynchus</t>
+  </si>
+  <si>
+    <t>Grampus_griseus</t>
+  </si>
+  <si>
+    <t>Sus scrofa</t>
+  </si>
+  <si>
+    <t>Sus_scrofa_domesticus</t>
+  </si>
+  <si>
+    <t>Lama_glama_domesticus</t>
+  </si>
+  <si>
+    <t>Equus_burchelli</t>
+  </si>
+  <si>
+    <t>Equus_caballus</t>
+  </si>
+  <si>
+    <t>Mustela putorius furo</t>
+  </si>
+  <si>
+    <t>Mustela_putorius</t>
+  </si>
+  <si>
+    <t>Procyon_lotor</t>
+  </si>
+  <si>
+    <t>Zalophus_californianus</t>
+  </si>
+  <si>
+    <t>Phoca_vitulina</t>
+  </si>
+  <si>
+    <t>Ursus_maritimus</t>
+  </si>
+  <si>
+    <t>Canis latrans</t>
+  </si>
+  <si>
+    <t>Canis_latrans</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Vulpes_vulpes</t>
+  </si>
+  <si>
+    <t>Panthera_leo</t>
+  </si>
+  <si>
+    <t>8.6999999999999993</t>
+  </si>
+  <si>
+    <t>Felis catus</t>
+  </si>
+  <si>
+    <t>Felis_catus</t>
+  </si>
+  <si>
+    <t>Crocuta_crocuta</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Cynictis_penicillata</t>
+  </si>
+  <si>
+    <t>Pteropus_giganteus*</t>
+  </si>
+  <si>
+    <t>Talpa_europaea</t>
+  </si>
+  <si>
+    <t>Galemys_pyrenaicus</t>
+  </si>
+  <si>
+    <t>Erinaceus_europaeus</t>
+  </si>
+  <si>
+    <t>Crocidura_flavescens</t>
+  </si>
+  <si>
+    <t>Crocidura_russala</t>
+  </si>
+  <si>
+    <t>Sorex_araneus</t>
+  </si>
+  <si>
+    <t>Sorex_minutus</t>
+  </si>
+  <si>
+    <t>Neomys_fodiens</t>
+  </si>
+  <si>
+    <t>Choloepus_didactylus*</t>
+  </si>
+  <si>
+    <t>Dasypus novemcinctus</t>
+  </si>
+  <si>
+    <t>Dasypus_novemcinctus*</t>
+  </si>
+  <si>
+    <t>Potamogale_velox</t>
+  </si>
+  <si>
+    <t>Elephantulus_fuscipes</t>
+  </si>
+  <si>
+    <t>Trichechus_manatus*</t>
+  </si>
+  <si>
+    <t>1.45</t>
+  </si>
+  <si>
+    <t>Procavia_capensis*</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Loxodonta_africana</t>
+  </si>
+  <si>
+    <t>19.5</t>
+  </si>
+  <si>
+    <t>Macropus_eugenii</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Macropus_fuliginosus</t>
+  </si>
+  <si>
+    <t>Macropus_rufogriseus</t>
+  </si>
+  <si>
+    <t>1.31</t>
+  </si>
+  <si>
+    <t>Didelphis_virginiana</t>
+  </si>
+  <si>
+    <t>¶ See Table S2 for column definitions</t>
+  </si>
+  <si>
+    <t>*Calculated from images of Nissl-stained coronal sections from www.brainmuseum.org (see Methods)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,218 +989,134 @@
   <dimension ref="A1:AO105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Body_weight</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Brain_weight_g</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Neonate_brain_weight_g</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Neocortex_mm^3</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>GI</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Ventricle_mm^3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Maximum_lifespan_yrs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Age_at_first_breeding_F_mnths</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Age_at_first_breeding_days</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Female_sexual_maturity_days</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Male_sexual_maturity_days</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Gestation_days</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Litter_size</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Litters_per_year</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Inter-litter_interval_days</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Weaning_period_days</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Weight_at_birth_g</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Weight_at_weaning_g</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Juvenility_primates_years</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Juvenility_days</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Max_home_range_ha</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>% Fruit and seeds</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Activity_timing</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Diet_breadth</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Trophic_level</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Population_group_size</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Social_group_size</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Adult_head_body_length_mm</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Age_at_eye_opening_days</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Altricial_precocial</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Basal_metabolic_rate</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Dispersal_age_days</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Habitat_breadth</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Social_system</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Glia_neuron_ratio</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Neuronal_density</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Glial_cell_density</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Neurogenic_period_days</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Phylo_rank</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Tachyglossus_aculeatus</t>
-        </is>
+    <row r="1" spans="1:41" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41">
+      <c r="B2" t="s">
+        <v>41</v>
       </c>
       <c r="C2">
         <v>4720</v>
@@ -615,10 +1166,8 @@
       <c r="AA2">
         <v>3</v>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC2" t="s">
+        <v>42</v>
       </c>
       <c r="AD2">
         <v>375</v>
@@ -633,16 +1182,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Mus musculus</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Mus_musculus</t>
-        </is>
+    <row r="3" spans="1:41">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
       </c>
       <c r="C3">
         <v>22.25</v>
@@ -732,16 +1277,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rattus_norvegicus</t>
-        </is>
+    <row r="4" spans="1:41">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
       </c>
       <c r="C4">
         <v>314.6666667</v>
@@ -825,11 +1366,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mesocricetus_auratus</t>
-        </is>
+    <row r="5" spans="1:41">
+      <c r="B5" t="s">
+        <v>47</v>
       </c>
       <c r="C5">
         <v>115</v>
@@ -910,11 +1449,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Castor_canadensis</t>
-        </is>
+    <row r="6" spans="1:41">
+      <c r="B6" t="s">
+        <v>48</v>
       </c>
       <c r="C6">
         <v>21750</v>
@@ -976,10 +1513,8 @@
       <c r="AA6">
         <v>1</v>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>5.0999999999999996</t>
-        </is>
+      <c r="AC6" t="s">
+        <v>49</v>
       </c>
       <c r="AD6">
         <v>754.74</v>
@@ -1000,11 +1535,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hydrochoerus_hydrochaeris</t>
-        </is>
+    <row r="7" spans="1:41">
+      <c r="B7" t="s">
+        <v>50</v>
       </c>
       <c r="C7">
         <v>42250</v>
@@ -1069,10 +1602,8 @@
       <c r="AA7">
         <v>1</v>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="AC7" t="s">
+        <v>51</v>
       </c>
       <c r="AD7">
         <v>1208.39</v>
@@ -1096,11 +1627,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Dasyprocta_leporina</t>
-        </is>
+    <row r="8" spans="1:41">
+      <c r="B8" t="s">
+        <v>52</v>
       </c>
       <c r="C8">
         <v>3265</v>
@@ -1172,16 +1701,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Oryctolagus cuniculus</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Oryctolagus_cuniculus*</t>
-        </is>
+    <row r="9" spans="1:41">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
       </c>
       <c r="C9">
         <v>2000</v>
@@ -1265,11 +1790,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Cercopithecus_mitis</t>
-        </is>
+    <row r="10" spans="1:41">
+      <c r="B10" t="s">
+        <v>55</v>
       </c>
       <c r="C10">
         <v>5041.29</v>
@@ -1328,10 +1851,8 @@
       <c r="AA10">
         <v>2</v>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="AC10" t="s">
+        <v>56</v>
       </c>
       <c r="AD10">
         <v>575</v>
@@ -1358,11 +1879,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Erythrocebus_patas</t>
-        </is>
+    <row r="11" spans="1:41">
+      <c r="B11" t="s">
+        <v>57</v>
       </c>
       <c r="C11">
         <v>7421.4</v>
@@ -1436,10 +1955,8 @@
       <c r="AB11">
         <v>20.5</v>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="AC11" t="s">
+        <v>58</v>
       </c>
       <c r="AD11">
         <v>665</v>
@@ -1463,11 +1980,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Miopithecus_talapoin</t>
-        </is>
+    <row r="12" spans="1:41">
+      <c r="B12" t="s">
+        <v>59</v>
       </c>
       <c r="C12">
         <v>1381</v>
@@ -1538,10 +2053,8 @@
       <c r="AB12">
         <v>66.5</v>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>91.2</t>
-        </is>
+      <c r="AC12" t="s">
+        <v>60</v>
       </c>
       <c r="AD12">
         <v>354.99</v>
@@ -1559,11 +2072,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Mandrillus_sphinx*</t>
-        </is>
+    <row r="13" spans="1:41">
+      <c r="B13" t="s">
+        <v>61</v>
       </c>
       <c r="C13">
         <v>12125</v>
@@ -1628,10 +2139,8 @@
       <c r="AB13">
         <v>30</v>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
+      <c r="AC13" t="s">
+        <v>62</v>
       </c>
       <c r="AD13">
         <v>758.9400000000001</v>
@@ -1655,11 +2164,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Lophocebus_albigena</t>
-        </is>
+    <row r="14" spans="1:41">
+      <c r="B14" t="s">
+        <v>63</v>
       </c>
       <c r="C14">
         <v>7992.75</v>
@@ -1730,10 +2237,8 @@
       <c r="AB14">
         <v>17</v>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="AC14" t="s">
+        <v>56</v>
       </c>
       <c r="AD14">
         <v>521.55</v>
@@ -1748,16 +2253,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Papio_hamadryas</t>
-        </is>
+    <row r="15" spans="1:41">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
       </c>
       <c r="C15">
         <v>16000</v>
@@ -1825,10 +2326,8 @@
       <c r="AB15">
         <v>54</v>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
+      <c r="AC15" t="s">
+        <v>66</v>
       </c>
       <c r="AD15">
         <v>675</v>
@@ -1846,16 +2345,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Macaca_mulatta</t>
-        </is>
+    <row r="16" spans="1:41">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
       </c>
       <c r="C16">
         <v>7102.833333</v>
@@ -1935,10 +2430,8 @@
       <c r="AB16">
         <v>48</v>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
+      <c r="AC16" t="s">
+        <v>69</v>
       </c>
       <c r="AD16">
         <v>555</v>
@@ -1968,11 +2461,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Piliocolobus_badius</t>
-        </is>
+    <row r="17" spans="1:41">
+      <c r="B17" t="s">
+        <v>70</v>
       </c>
       <c r="C17">
         <v>7854.833333</v>
@@ -2010,10 +2501,8 @@
       <c r="Y17">
         <v>3</v>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>&gt;10</t>
-        </is>
+      <c r="AC17" t="s">
+        <v>71</v>
       </c>
       <c r="AF17">
         <v>2</v>
@@ -2025,11 +2514,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Pygathrix_nemaeus</t>
-        </is>
+    <row r="18" spans="1:41">
+      <c r="B18" t="s">
+        <v>72</v>
       </c>
       <c r="C18">
         <v>8481.666667</v>
@@ -2091,10 +2578,8 @@
       <c r="AB18">
         <v>9.300000000000001</v>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>9.3000000000000007</t>
-        </is>
+      <c r="AC18" t="s">
+        <v>73</v>
       </c>
       <c r="AD18">
         <v>326.37</v>
@@ -2109,16 +2594,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla gorilla</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Gorilla_gorilla</t>
-        </is>
+    <row r="19" spans="1:41">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
       </c>
       <c r="C19">
         <v>99648.39999999999</v>
@@ -2195,10 +2676,8 @@
       <c r="AB19">
         <v>10</v>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AC19" t="s">
+        <v>76</v>
       </c>
       <c r="AD19">
         <v>1594.44</v>
@@ -2228,16 +2707,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Homo_sapiens</t>
-        </is>
+    <row r="20" spans="1:41">
+      <c r="A20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
       </c>
       <c r="C20">
         <v>61770.315</v>
@@ -2330,16 +2805,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Pan_troglodytes</t>
-        </is>
+    <row r="21" spans="1:41">
+      <c r="A21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" t="s">
+        <v>80</v>
       </c>
       <c r="C21">
         <v>41057.09091</v>
@@ -2419,10 +2890,8 @@
       <c r="AB21">
         <v>45</v>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="AC21" t="s">
+        <v>81</v>
       </c>
       <c r="AD21">
         <v>796.09</v>
@@ -2455,11 +2924,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Pongo_pygmaeus</t>
-        </is>
+    <row r="22" spans="1:41">
+      <c r="B22" t="s">
+        <v>82</v>
       </c>
       <c r="C22">
         <v>42447.66667</v>
@@ -2533,10 +3000,8 @@
       <c r="AB22">
         <v>1</v>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC22" t="s">
+        <v>42</v>
       </c>
       <c r="AD22">
         <v>890</v>
@@ -2563,11 +3028,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hylobates_lar</t>
-        </is>
+    <row r="23" spans="1:41">
+      <c r="B23" t="s">
+        <v>83</v>
       </c>
       <c r="C23">
         <v>5724.857143</v>
@@ -2644,10 +3107,8 @@
       <c r="AA23">
         <v>2</v>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+      <c r="AC23" t="s">
+        <v>84</v>
       </c>
       <c r="AD23">
         <v>545</v>
@@ -2662,11 +3123,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Alouatta_palliata*</t>
-        </is>
+    <row r="24" spans="1:41">
+      <c r="B24" t="s">
+        <v>85</v>
       </c>
       <c r="C24">
         <v>5892.8</v>
@@ -2731,10 +3190,8 @@
       <c r="AA24">
         <v>1</v>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
+      <c r="AC24" t="s">
+        <v>86</v>
       </c>
       <c r="AD24">
         <v>576.35</v>
@@ -2764,11 +3221,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Alouatta_seniculus</t>
-        </is>
+    <row r="25" spans="1:41">
+      <c r="B25" t="s">
+        <v>87</v>
       </c>
       <c r="C25">
         <v>5889.571429</v>
@@ -2830,10 +3285,8 @@
       <c r="AA25">
         <v>2</v>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
+      <c r="AC25" t="s">
+        <v>88</v>
       </c>
       <c r="AD25">
         <v>560.21</v>
@@ -2851,11 +3304,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Ateles_paniscus</t>
-        </is>
+    <row r="26" spans="1:41">
+      <c r="B26" t="s">
+        <v>89</v>
       </c>
       <c r="C26">
         <v>8447.428571</v>
@@ -2920,10 +3371,8 @@
       <c r="AA26">
         <v>2</v>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="AC26" t="s">
+        <v>90</v>
       </c>
       <c r="AD26">
         <v>575.96</v>
@@ -2938,11 +3387,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Lagothrix_lagothricha</t>
-        </is>
+    <row r="27" spans="1:41">
+      <c r="B27" t="s">
+        <v>91</v>
       </c>
       <c r="C27">
         <v>5959</v>
@@ -3013,10 +3460,8 @@
       <c r="AA27">
         <v>2</v>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="AC27" t="s">
+        <v>92</v>
       </c>
       <c r="AD27">
         <v>536.39</v>
@@ -3034,11 +3479,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Callicebus_moloch*</t>
-        </is>
+    <row r="28" spans="1:41">
+      <c r="B28" t="s">
+        <v>93</v>
       </c>
       <c r="C28">
         <v>980</v>
@@ -3097,10 +3540,8 @@
       <c r="AA28">
         <v>2</v>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="AC28" t="s">
+        <v>94</v>
       </c>
       <c r="AD28">
         <v>358.65</v>
@@ -3127,16 +3568,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Aotus nancymaae</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Aotus_trivirgatus</t>
-        </is>
+    <row r="29" spans="1:41">
+      <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
       </c>
       <c r="C29">
         <v>783.6</v>
@@ -3213,10 +3650,8 @@
       <c r="AA29">
         <v>2</v>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
+      <c r="AC29" t="s">
+        <v>97</v>
       </c>
       <c r="AD29">
         <v>357.99</v>
@@ -3246,11 +3681,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Callimico_goeldii</t>
-        </is>
+    <row r="30" spans="1:41">
+      <c r="B30" t="s">
+        <v>98</v>
       </c>
       <c r="C30">
         <v>492.2</v>
@@ -3324,10 +3757,8 @@
       <c r="AA30">
         <v>2</v>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>6.85</t>
-        </is>
+      <c r="AC30" t="s">
+        <v>99</v>
       </c>
       <c r="AD30">
         <v>280</v>
@@ -3345,16 +3776,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Callithrix_jacchus</t>
-        </is>
+    <row r="31" spans="1:41">
+      <c r="A31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" t="s">
+        <v>101</v>
       </c>
       <c r="C31">
         <v>288.12</v>
@@ -3431,10 +3858,8 @@
       <c r="AA31">
         <v>2</v>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>8.5500000000000007</t>
-        </is>
+      <c r="AC31" t="s">
+        <v>102</v>
       </c>
       <c r="AF31">
         <v>2</v>
@@ -3455,11 +3880,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Saguinus_midas</t>
-        </is>
+    <row r="32" spans="1:41">
+      <c r="B32" t="s">
+        <v>103</v>
       </c>
       <c r="C32">
         <v>439.2</v>
@@ -3524,10 +3947,8 @@
       <c r="AA32">
         <v>2</v>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>5.55</t>
-        </is>
+      <c r="AC32" t="s">
+        <v>104</v>
       </c>
       <c r="AD32">
         <v>264.21</v>
@@ -3539,11 +3960,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Saguinus_oedipus</t>
-        </is>
+    <row r="33" spans="1:41">
+      <c r="B33" t="s">
+        <v>105</v>
       </c>
       <c r="C33">
         <v>368.8333333</v>
@@ -3608,10 +4027,8 @@
       <c r="AA33">
         <v>2</v>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
+      <c r="AC33" t="s">
+        <v>106</v>
       </c>
       <c r="AD33">
         <v>239.99</v>
@@ -3638,11 +4055,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Cebus_albifrons</t>
-        </is>
+    <row r="34" spans="1:41">
+      <c r="B34" t="s">
+        <v>107</v>
       </c>
       <c r="C34">
         <v>2482.8</v>
@@ -3713,10 +4128,8 @@
       <c r="AA34">
         <v>2</v>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="AC34" t="s">
+        <v>108</v>
       </c>
       <c r="AD34">
         <v>384.28</v>
@@ -3734,16 +4147,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Saimiri boliviensis boliviensis</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Saimiri_sciureus</t>
-        </is>
+    <row r="35" spans="1:41">
+      <c r="A35" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" t="s">
+        <v>110</v>
       </c>
       <c r="C35">
         <v>680.6</v>
@@ -3817,10 +4226,8 @@
       <c r="AA35">
         <v>2</v>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>36.090000000000003</t>
-        </is>
+      <c r="AC35" t="s">
+        <v>111</v>
       </c>
       <c r="AD35">
         <v>322</v>
@@ -3850,11 +4257,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Tarsius_bancanus</t>
-        </is>
+    <row r="36" spans="1:41">
+      <c r="B36" t="s">
+        <v>112</v>
       </c>
       <c r="C36">
         <v>115.875</v>
@@ -3913,10 +4318,8 @@
       <c r="AA36">
         <v>2</v>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC36" t="s">
+        <v>42</v>
       </c>
       <c r="AD36">
         <v>106.59</v>
@@ -3940,11 +4343,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Tarsius_syrichta</t>
-        </is>
+    <row r="37" spans="1:41">
+      <c r="B37" t="s">
+        <v>113</v>
       </c>
       <c r="C37">
         <v>112.05</v>
@@ -3997,10 +4398,8 @@
       <c r="AA37">
         <v>1</v>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC37" t="s">
+        <v>42</v>
       </c>
       <c r="AD37">
         <v>117.74</v>
@@ -4027,16 +4426,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Microcebus murinus</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Microcebus_murinus</t>
-        </is>
+    <row r="38" spans="1:41">
+      <c r="A38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" t="s">
+        <v>115</v>
       </c>
       <c r="C38">
         <v>71.828</v>
@@ -4110,10 +4505,8 @@
       <c r="AB38">
         <v>3.5</v>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC38" t="s">
+        <v>42</v>
       </c>
       <c r="AD38">
         <v>143.61</v>
@@ -4143,11 +4536,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Cheirogaleus_major</t>
-        </is>
+    <row r="39" spans="1:41">
+      <c r="B39" t="s">
+        <v>116</v>
       </c>
       <c r="C39">
         <v>433.25</v>
@@ -4206,10 +4597,8 @@
       <c r="AB39">
         <v>1</v>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC39" t="s">
+        <v>42</v>
       </c>
       <c r="AD39">
         <v>225</v>
@@ -4227,11 +4616,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Cheirogaleus_medius</t>
-        </is>
+    <row r="40" spans="1:41">
+      <c r="B40" t="s">
+        <v>117</v>
       </c>
       <c r="C40">
         <v>214</v>
@@ -4302,10 +4689,8 @@
       <c r="AB40">
         <v>1</v>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC40" t="s">
+        <v>42</v>
       </c>
       <c r="AD40">
         <v>225</v>
@@ -4335,11 +4720,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Avahi_laniger</t>
-        </is>
+    <row r="41" spans="1:41">
+      <c r="B41" t="s">
+        <v>118</v>
       </c>
       <c r="C41">
         <v>1200.1428</v>
@@ -4395,10 +4778,8 @@
       <c r="AA41">
         <v>1</v>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AC41" t="s">
+        <v>119</v>
       </c>
       <c r="AD41">
         <v>275</v>
@@ -4416,11 +4797,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Avahi_occidentalis</t>
-        </is>
+    <row r="42" spans="1:41">
+      <c r="B42" t="s">
+        <v>120</v>
       </c>
       <c r="C42">
         <v>832.333</v>
@@ -4455,10 +4834,8 @@
       <c r="AA42">
         <v>1</v>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AC42" t="s">
+        <v>121</v>
       </c>
       <c r="AF42">
         <v>2</v>
@@ -4473,11 +4850,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Propithecus_verreauxi</t>
-        </is>
+    <row r="43" spans="1:41">
+      <c r="B43" t="s">
+        <v>122</v>
       </c>
       <c r="C43">
         <v>3547.125</v>
@@ -4554,10 +4929,8 @@
       <c r="AB43">
         <v>7.5</v>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
+      <c r="AC43" t="s">
+        <v>123</v>
       </c>
       <c r="AD43">
         <v>472.49</v>
@@ -4578,11 +4951,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Indri_indri</t>
-        </is>
+    <row r="44" spans="1:41">
+      <c r="B44" t="s">
+        <v>124</v>
       </c>
       <c r="C44">
         <v>7410.8333</v>
@@ -4653,10 +5024,8 @@
       <c r="AB44">
         <v>3.5</v>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
+      <c r="AC44" t="s">
+        <v>125</v>
       </c>
       <c r="AD44">
         <v>734.99</v>
@@ -4671,11 +5040,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Daubentonia_madagascariensis</t>
-        </is>
+    <row r="45" spans="1:41">
+      <c r="B45" t="s">
+        <v>126</v>
       </c>
       <c r="C45">
         <v>2640.285</v>
@@ -4749,10 +5116,8 @@
       <c r="AB45">
         <v>1</v>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC45" t="s">
+        <v>42</v>
       </c>
       <c r="AD45">
         <v>400</v>
@@ -4770,11 +5135,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Eulemur_fulvus</t>
-        </is>
+    <row r="46" spans="1:41">
+      <c r="B46" t="s">
+        <v>127</v>
       </c>
       <c r="C46">
         <v>1933.8</v>
@@ -4848,10 +5211,8 @@
       <c r="AB46">
         <v>9.25</v>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>9.15</t>
-        </is>
+      <c r="AC46" t="s">
+        <v>128</v>
       </c>
       <c r="AD46">
         <v>469.62</v>
@@ -4869,11 +5230,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Eulemur_mongoz</t>
-        </is>
+    <row r="47" spans="1:41">
+      <c r="B47" t="s">
+        <v>129</v>
       </c>
       <c r="C47">
         <v>1632.75</v>
@@ -4941,10 +5300,8 @@
       <c r="AB47">
         <v>4</v>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
+      <c r="AC47" t="s">
+        <v>130</v>
       </c>
       <c r="AD47">
         <v>354.85</v>
@@ -4971,11 +5328,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Lemur_catta</t>
-        </is>
+    <row r="48" spans="1:41">
+      <c r="B48" t="s">
+        <v>131</v>
       </c>
       <c r="C48">
         <v>2264.25</v>
@@ -5049,10 +5404,8 @@
       <c r="AB48">
         <v>15</v>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>16.45</t>
-        </is>
+      <c r="AC48" t="s">
+        <v>132</v>
       </c>
       <c r="AD48">
         <v>425</v>
@@ -5082,11 +5435,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Varecia_variegata</t>
-        </is>
+    <row r="49" spans="1:41">
+      <c r="B49" t="s">
+        <v>133</v>
       </c>
       <c r="C49">
         <v>3344.857</v>
@@ -5163,10 +5514,8 @@
       <c r="AB49">
         <v>3.5</v>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
+      <c r="AC49" t="s">
+        <v>134</v>
       </c>
       <c r="AD49">
         <v>547.35</v>
@@ -5187,11 +5536,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Lepilemur_ruficaudatus</t>
-        </is>
+    <row r="50" spans="1:41">
+      <c r="B50" t="s">
+        <v>135</v>
       </c>
       <c r="C50">
         <v>821.8933</v>
@@ -5250,10 +5597,8 @@
       <c r="AA50">
         <v>1</v>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC50" t="s">
+        <v>42</v>
       </c>
       <c r="AF50">
         <v>2</v>
@@ -5265,11 +5610,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Perodicticus_potto</t>
-        </is>
+    <row r="51" spans="1:41">
+      <c r="B51" t="s">
+        <v>136</v>
       </c>
       <c r="C51">
         <v>1008.4285</v>
@@ -5340,10 +5683,8 @@
       <c r="AA51">
         <v>2</v>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC51" t="s">
+        <v>42</v>
       </c>
       <c r="AD51">
         <v>320</v>
@@ -5364,11 +5705,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Loris_tardigradus</t>
-        </is>
+    <row r="52" spans="1:41">
+      <c r="B52" t="s">
+        <v>137</v>
       </c>
       <c r="C52">
         <v>281.44</v>
@@ -5445,10 +5784,8 @@
       <c r="AA52">
         <v>2</v>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC52" t="s">
+        <v>42</v>
       </c>
       <c r="AD52">
         <v>224.49</v>
@@ -5469,11 +5806,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Nycticebus_coucang</t>
-        </is>
+    <row r="53" spans="1:41">
+      <c r="B53" t="s">
+        <v>138</v>
       </c>
       <c r="C53">
         <v>828.1875</v>
@@ -5547,10 +5882,8 @@
       <c r="AA53">
         <v>2</v>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC53" t="s">
+        <v>42</v>
       </c>
       <c r="AD53">
         <v>300</v>
@@ -5580,11 +5913,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Galago_senegalensis</t>
-        </is>
+    <row r="54" spans="1:41">
+      <c r="B54" t="s">
+        <v>139</v>
       </c>
       <c r="C54">
         <v>178.7</v>
@@ -5661,10 +5992,8 @@
       <c r="AA54">
         <v>2</v>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+      <c r="AC54" t="s">
+        <v>140</v>
       </c>
       <c r="AD54">
         <v>160</v>
@@ -5691,16 +6020,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Otolemur garnettii</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Otolemur_crassicaudatus</t>
-        </is>
+    <row r="55" spans="1:41">
+      <c r="A55" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" t="s">
+        <v>142</v>
       </c>
       <c r="C55">
         <v>952.428</v>
@@ -5777,10 +6102,8 @@
       <c r="AA55">
         <v>2</v>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+      <c r="AC55" t="s">
+        <v>140</v>
       </c>
       <c r="AD55">
         <v>307</v>
@@ -5798,11 +6121,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Galago_demidoff</t>
-        </is>
+    <row r="56" spans="1:41">
+      <c r="B56" t="s">
+        <v>143</v>
       </c>
       <c r="C56">
         <v>71.5</v>
@@ -5870,10 +6191,8 @@
       <c r="AA56">
         <v>2</v>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
+      <c r="AC56" t="s">
+        <v>144</v>
       </c>
       <c r="AD56">
         <v>120</v>
@@ -5891,11 +6210,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Cynocephalus_volans*</t>
-        </is>
+    <row r="57" spans="1:41">
+      <c r="B57" t="s">
+        <v>145</v>
       </c>
       <c r="C57">
         <v>1300</v>
@@ -5940,16 +6257,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Tupaia belangeri</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Tupaia_glis*</t>
-        </is>
+    <row r="58" spans="1:41">
+      <c r="A58" t="s">
+        <v>146</v>
+      </c>
+      <c r="B58" t="s">
+        <v>147</v>
       </c>
       <c r="C58">
         <v>173.3333333</v>
@@ -6039,11 +6352,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Ovis_aries</t>
-        </is>
+    <row r="59" spans="1:41">
+      <c r="B59" t="s">
+        <v>148</v>
       </c>
       <c r="C59">
         <v>63966.66667</v>
@@ -6118,11 +6429,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Capra_hircus_domestica*</t>
-        </is>
+    <row r="60" spans="1:41">
+      <c r="B60" t="s">
+        <v>149</v>
       </c>
       <c r="C60">
         <v>38111.111</v>
@@ -6194,11 +6503,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Bos_taurus_indicus</t>
-        </is>
+    <row r="61" spans="1:41">
+      <c r="B61" t="s">
+        <v>150</v>
       </c>
       <c r="C61">
         <v>596666.6666999999</v>
@@ -6240,11 +6547,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Odocoileus_virginiatus</t>
-        </is>
+    <row r="62" spans="1:41">
+      <c r="B62" t="s">
+        <v>151</v>
       </c>
       <c r="C62">
         <v>87000</v>
@@ -6306,10 +6611,8 @@
       <c r="AA62">
         <v>1</v>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="AC62" t="s">
+        <v>152</v>
       </c>
       <c r="AD62">
         <v>1513.69</v>
@@ -6324,11 +6627,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Phocoena_phocoena</t>
-        </is>
+    <row r="63" spans="1:41">
+      <c r="B63" t="s">
+        <v>153</v>
       </c>
       <c r="C63">
         <v>55500</v>
@@ -6390,10 +6691,8 @@
       <c r="AB63">
         <v>4</v>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="AC63" t="s">
+        <v>154</v>
       </c>
       <c r="AD63">
         <v>1530.07</v>
@@ -6408,11 +6707,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Delphinus_delphis</t>
-        </is>
+    <row r="64" spans="1:41">
+      <c r="B64" t="s">
+        <v>155</v>
       </c>
       <c r="C64">
         <v>80000</v>
@@ -6472,11 +6769,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Tursiops_truncatus</t>
-        </is>
+    <row r="65" spans="1:41">
+      <c r="B65" t="s">
+        <v>156</v>
       </c>
       <c r="C65">
         <v>177500</v>
@@ -6538,10 +6833,8 @@
       <c r="AB65">
         <v>7</v>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="AC65" t="s">
+        <v>51</v>
       </c>
       <c r="AD65">
         <v>3257.91</v>
@@ -6568,11 +6861,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Pseudorca_crassidens</t>
-        </is>
+    <row r="66" spans="1:41">
+      <c r="B66" t="s">
+        <v>157</v>
       </c>
       <c r="C66">
         <v>1360000</v>
@@ -6626,11 +6917,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Globicephala_macrorhynchus</t>
-        </is>
+    <row r="67" spans="1:41">
+      <c r="B67" t="s">
+        <v>158</v>
       </c>
       <c r="C67">
         <v>725999.99</v>
@@ -6690,11 +6979,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Grampus_griseus</t>
-        </is>
+    <row r="68" spans="1:41">
+      <c r="B68" t="s">
+        <v>159</v>
       </c>
       <c r="C68">
         <v>425000</v>
@@ -6733,16 +7020,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Sus scrofa</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Sus_scrofa_domesticus</t>
-        </is>
+    <row r="69" spans="1:41">
+      <c r="A69" t="s">
+        <v>160</v>
+      </c>
+      <c r="B69" t="s">
+        <v>161</v>
       </c>
       <c r="C69">
         <v>133600</v>
@@ -6796,11 +7079,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Lama_glama_domesticus</t>
-        </is>
+    <row r="70" spans="1:41">
+      <c r="B70" t="s">
+        <v>162</v>
       </c>
       <c r="C70">
         <v>107250</v>
@@ -6872,11 +7153,9 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Equus_burchelli</t>
-        </is>
+    <row r="71" spans="1:41">
+      <c r="B71" t="s">
+        <v>163</v>
       </c>
       <c r="C71">
         <v>280000</v>
@@ -6948,11 +7227,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Equus_caballus</t>
-        </is>
+    <row r="72" spans="1:41">
+      <c r="B72" t="s">
+        <v>164</v>
       </c>
       <c r="C72">
         <v>367000</v>
@@ -7027,16 +7304,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Mustela putorius furo</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Mustela_putorius</t>
-        </is>
+    <row r="73" spans="1:41">
+      <c r="A73" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" t="s">
+        <v>166</v>
       </c>
       <c r="C73">
         <v>809</v>
@@ -7111,11 +7384,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Procyon_lotor</t>
-        </is>
+    <row r="74" spans="1:41">
+      <c r="B74" t="s">
+        <v>167</v>
       </c>
       <c r="C74">
         <v>5916.25</v>
@@ -7171,10 +7442,8 @@
       <c r="AA74">
         <v>2</v>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC74" t="s">
+        <v>42</v>
       </c>
       <c r="AD74">
         <v>484.68</v>
@@ -7210,11 +7479,9 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Zalophus_californianus</t>
-        </is>
+    <row r="75" spans="1:41">
+      <c r="B75" t="s">
+        <v>168</v>
       </c>
       <c r="C75">
         <v>140000</v>
@@ -7301,11 +7568,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Phoca_vitulina</t>
-        </is>
+    <row r="76" spans="1:41">
+      <c r="B76" t="s">
+        <v>169</v>
       </c>
       <c r="C76">
         <v>115000</v>
@@ -7386,11 +7651,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Ursus_maritimus</t>
-        </is>
+    <row r="77" spans="1:41">
+      <c r="B77" t="s">
+        <v>170</v>
       </c>
       <c r="C77">
         <v>340635</v>
@@ -7458,10 +7721,8 @@
       <c r="AB77">
         <v>1</v>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC77" t="s">
+        <v>42</v>
       </c>
       <c r="AD77">
         <v>1992.55</v>
@@ -7497,16 +7758,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Canis latrans</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Canis_latrans</t>
-        </is>
+    <row r="78" spans="1:41">
+      <c r="A78" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" t="s">
+        <v>172</v>
       </c>
       <c r="C78">
         <v>10750</v>
@@ -7568,10 +7825,8 @@
       <c r="AA78">
         <v>3</v>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
+      <c r="AC78" t="s">
+        <v>173</v>
       </c>
       <c r="AD78">
         <v>872.39</v>
@@ -7607,11 +7862,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Vulpes_vulpes</t>
-        </is>
+    <row r="79" spans="1:41">
+      <c r="B79" t="s">
+        <v>174</v>
       </c>
       <c r="C79">
         <v>4634.4</v>
@@ -7676,10 +7929,8 @@
       <c r="AA79">
         <v>3</v>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AC79" t="s">
+        <v>121</v>
       </c>
       <c r="AD79">
         <v>627.12</v>
@@ -7715,11 +7966,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Panthera_leo</t>
-        </is>
+    <row r="80" spans="1:41">
+      <c r="B80" t="s">
+        <v>175</v>
       </c>
       <c r="C80">
         <v>161833.3333</v>
@@ -7784,10 +8033,8 @@
       <c r="AA80">
         <v>3</v>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>8.6999999999999993</t>
-        </is>
+      <c r="AC80" t="s">
+        <v>176</v>
       </c>
       <c r="AD80">
         <v>1835.16</v>
@@ -7814,16 +8061,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Felis catus</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Felis_catus</t>
-        </is>
+    <row r="81" spans="1:41">
+      <c r="A81" t="s">
+        <v>177</v>
+      </c>
+      <c r="B81" t="s">
+        <v>178</v>
       </c>
       <c r="C81">
         <v>3183.333333</v>
@@ -7895,11 +8138,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Crocuta_crocuta</t>
-        </is>
+    <row r="82" spans="1:41">
+      <c r="B82" t="s">
+        <v>179</v>
       </c>
       <c r="C82">
         <v>63000</v>
@@ -7952,10 +8193,8 @@
       <c r="AA82">
         <v>3</v>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="AC82" t="s">
+        <v>180</v>
       </c>
       <c r="AD82">
         <v>1300.11</v>
@@ -7988,11 +8227,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Cynictis_penicillata</t>
-        </is>
+    <row r="83" spans="1:41">
+      <c r="B83" t="s">
+        <v>181</v>
       </c>
       <c r="C83">
         <v>627.3033333</v>
@@ -8067,11 +8304,9 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Pteropus_giganteus*</t>
-        </is>
+    <row r="84" spans="1:41">
+      <c r="B84" t="s">
+        <v>182</v>
       </c>
       <c r="C84">
         <v>1038.75</v>
@@ -8146,11 +8381,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Talpa_europaea</t>
-        </is>
+    <row r="85" spans="1:41">
+      <c r="B85" t="s">
+        <v>183</v>
       </c>
       <c r="C85">
         <v>92.5</v>
@@ -8215,10 +8448,8 @@
       <c r="AB85">
         <v>1</v>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC85" t="s">
+        <v>42</v>
       </c>
       <c r="AD85">
         <v>129.99</v>
@@ -8239,11 +8470,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Galemys_pyrenaicus</t>
-        </is>
+    <row r="86" spans="1:41">
+      <c r="B86" t="s">
+        <v>184</v>
       </c>
       <c r="C86">
         <v>57.5</v>
@@ -8287,10 +8516,8 @@
       <c r="AB86">
         <v>1.5</v>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC86" t="s">
+        <v>42</v>
       </c>
       <c r="AD86">
         <v>125</v>
@@ -8302,11 +8529,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Erinaceus_europaeus</t>
-        </is>
+    <row r="87" spans="1:41">
+      <c r="B87" t="s">
+        <v>185</v>
       </c>
       <c r="C87">
         <v>801</v>
@@ -8368,10 +8593,8 @@
       <c r="AA87">
         <v>2</v>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC87" t="s">
+        <v>42</v>
       </c>
       <c r="AD87">
         <v>237.17</v>
@@ -8401,11 +8624,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Crocidura_flavescens</t>
-        </is>
+    <row r="88" spans="1:41">
+      <c r="B88" t="s">
+        <v>186</v>
       </c>
       <c r="C88">
         <v>45</v>
@@ -8447,11 +8668,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Crocidura_russala</t>
-        </is>
+    <row r="89" spans="1:41">
+      <c r="B89" t="s">
+        <v>187</v>
       </c>
       <c r="C89">
         <v>11.6</v>
@@ -8532,11 +8751,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Sorex_araneus</t>
-        </is>
+    <row r="90" spans="1:41">
+      <c r="B90" t="s">
+        <v>188</v>
       </c>
       <c r="C90">
         <v>9</v>
@@ -8592,10 +8809,8 @@
       <c r="AB90">
         <v>1</v>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC90" t="s">
+        <v>42</v>
       </c>
       <c r="AD90">
         <v>72.78</v>
@@ -8625,11 +8840,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Sorex_minutus</t>
-        </is>
+    <row r="91" spans="1:41">
+      <c r="B91" t="s">
+        <v>189</v>
       </c>
       <c r="C91">
         <v>7.2</v>
@@ -8688,10 +8901,8 @@
       <c r="AB91">
         <v>1</v>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC91" t="s">
+        <v>42</v>
       </c>
       <c r="AD91">
         <v>57.11</v>
@@ -8703,11 +8914,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Neomys_fodiens</t>
-        </is>
+    <row r="92" spans="1:41">
+      <c r="B92" t="s">
+        <v>190</v>
       </c>
       <c r="C92">
         <v>15</v>
@@ -8763,10 +8972,8 @@
       <c r="AB92">
         <v>1</v>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC92" t="s">
+        <v>42</v>
       </c>
       <c r="AD92">
         <v>81.94</v>
@@ -8790,11 +8997,9 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Choloepus_didactylus*</t>
-        </is>
+    <row r="93" spans="1:41">
+      <c r="B93" t="s">
+        <v>191</v>
       </c>
       <c r="C93">
         <v>6250</v>
@@ -8841,10 +9046,8 @@
       <c r="AA93">
         <v>2</v>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC93" t="s">
+        <v>42</v>
       </c>
       <c r="AD93">
         <v>686.96</v>
@@ -8865,16 +9068,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Dasypus novemcinctus</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Dasypus_novemcinctus*</t>
-        </is>
+    <row r="94" spans="1:41">
+      <c r="A94" t="s">
+        <v>192</v>
+      </c>
+      <c r="B94" t="s">
+        <v>193</v>
       </c>
       <c r="C94">
         <v>3762</v>
@@ -8933,10 +9132,8 @@
       <c r="AA94">
         <v>2</v>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC94" t="s">
+        <v>42</v>
       </c>
       <c r="AD94">
         <v>442.79</v>
@@ -8957,11 +9154,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Potamogale_velox</t>
-        </is>
+    <row r="95" spans="1:41">
+      <c r="B95" t="s">
+        <v>194</v>
       </c>
       <c r="C95">
         <v>670.99</v>
@@ -8990,10 +9185,8 @@
       <c r="AB95">
         <v>1</v>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC95" t="s">
+        <v>42</v>
       </c>
       <c r="AD95">
         <v>320</v>
@@ -9005,11 +9198,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Elephantulus_fuscipes</t>
-        </is>
+    <row r="96" spans="1:41">
+      <c r="B96" t="s">
+        <v>195</v>
       </c>
       <c r="C96">
         <v>57</v>
@@ -9027,11 +9218,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Trichechus_manatus*</t>
-        </is>
+    <row r="97" spans="2:41">
+      <c r="B97" t="s">
+        <v>196</v>
       </c>
       <c r="C97">
         <v>797000</v>
@@ -9078,10 +9267,8 @@
       <c r="AA97">
         <v>2</v>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="AC97" t="s">
+        <v>197</v>
       </c>
       <c r="AD97">
         <v>3354.92</v>
@@ -9108,11 +9295,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Procavia_capensis*</t>
-        </is>
+    <row r="98" spans="2:41">
+      <c r="B98" t="s">
+        <v>198</v>
       </c>
       <c r="C98">
         <v>3420</v>
@@ -9180,10 +9365,8 @@
       <c r="AB98">
         <v>80</v>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="AC98" t="s">
+        <v>199</v>
       </c>
       <c r="AD98">
         <v>467.37</v>
@@ -9207,11 +9390,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Loxodonta_africana</t>
-        </is>
+    <row r="99" spans="2:41">
+      <c r="B99" t="s">
+        <v>200</v>
       </c>
       <c r="C99">
         <v>3775000</v>
@@ -9276,10 +9457,8 @@
       <c r="AA99">
         <v>1</v>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
+      <c r="AC99" t="s">
+        <v>201</v>
       </c>
       <c r="AE99">
         <v>0</v>
@@ -9294,11 +9473,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Macropus_eugenii</t>
-        </is>
+    <row r="100" spans="2:41">
+      <c r="B100" t="s">
+        <v>202</v>
       </c>
       <c r="C100">
         <v>6500</v>
@@ -9348,10 +9525,8 @@
       <c r="V100">
         <v>4.375</v>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="AC100" t="s">
+        <v>203</v>
       </c>
       <c r="AG100">
         <v>1385.65</v>
@@ -9363,11 +9538,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Macropus_fuliginosus</t>
-        </is>
+    <row r="101" spans="2:41">
+      <c r="B101" t="s">
+        <v>204</v>
       </c>
       <c r="C101">
         <v>29625</v>
@@ -9430,11 +9603,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Macropus_rufogriseus</t>
-        </is>
+    <row r="102" spans="2:41">
+      <c r="B102" t="s">
+        <v>205</v>
       </c>
       <c r="C102">
         <v>15700</v>
@@ -9490,10 +9661,8 @@
       <c r="Y102">
         <v>1</v>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
+      <c r="AC102" t="s">
+        <v>206</v>
       </c>
       <c r="AE102">
         <v>153.5</v>
@@ -9505,11 +9674,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Didelphis_virginiana</t>
-        </is>
+    <row r="103" spans="2:41">
+      <c r="B103" t="s">
+        <v>207</v>
       </c>
       <c r="C103">
         <v>3000</v>
@@ -9571,10 +9738,8 @@
       <c r="AA103">
         <v>2</v>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AC103" t="s">
+        <v>42</v>
       </c>
       <c r="AG103">
         <v>719.0700000000001</v>
@@ -9592,18 +9757,14 @@
         <v>102</v>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>¶ See Table S2 for column definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>*Calculated from images of Nissl-stained coronal sections from www.brainmuseum.org (see Methods)</t>
-        </is>
+    <row r="104" spans="2:41">
+      <c r="B104" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="105" spans="2:41">
+      <c r="B105" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -9887,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD278CA0-F517-4389-9898-351629961DB5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D88707D4-C436-4249-A001-A74AEA954D12}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4BD0F19-144F-4FB9-9E7A-3A0BCF9A09F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FE9BE0B-F786-4A33-A50A-A90FFD05CF70}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{189146BE-7A7B-461E-AA14-CE97262A31DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9160962-A215-4D5A-AEA1-642992310124}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D88707D4-C436-4249-A001-A74AEA954D12}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F864A774-3085-4A30-860D-96DB3D6C6E89}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FE9BE0B-F786-4A33-A50A-A90FFD05CF70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B789EA8E-8F2A-4EA8-B106-E74E73720EEE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9160962-A215-4D5A-AEA1-642992310124}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46BF8BE3-D90F-4F6F-9486-DD4FF094A540}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F864A774-3085-4A30-860D-96DB3D6C6E89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0DE63BE-3FE0-4045-8D36-3A74BBFA56EC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B789EA8E-8F2A-4EA8-B106-E74E73720EEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5DBD923-4BF6-4223-B256-F4CCE7400265}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46BF8BE3-D90F-4F6F-9486-DD4FF094A540}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED652395-FECC-457D-ADD1-E9891571182F}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,291 +9770,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0DE63BE-3FE0-4045-8D36-3A74BBFA56EC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5DBD923-4BF6-4223-B256-F4CCE7400265}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED652395-FECC-457D-ADD1-E9891571182F}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,4 +9770,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFE12F9D-18F7-40A2-8B25-E8B59A3DB6D9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5465F9FD-A2D1-4456-A18D-58D7C1209312}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D5FF5A-1F5A-45D5-977B-5023CD9DB67A}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,291 +9770,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFE12F9D-18F7-40A2-8B25-E8B59A3DB6D9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5465F9FD-A2D1-4456-A18D-58D7C1209312}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D5FF5A-1F5A-45D5-977B-5023CD9DB67A}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,4 +9770,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C55B63DB-3ED2-4ED8-B6F3-4955FC0CD574}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B4B143-0E32-41AD-B855-C8A2AA914FCA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1E2C459-78F4-4AAB-A8A1-6D6D7E7F3BAA}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C55B63DB-3ED2-4ED8-B6F3-4955FC0CD574}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEC2031C-FFB3-4074-9513-9896DAD6DD1C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B4B143-0E32-41AD-B855-C8A2AA914FCA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AE42273-4C11-4D3A-95B0-D6B50E30E8BA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1E2C459-78F4-4AAB-A8A1-6D6D7E7F3BAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D914FE5A-C7A1-4BB0-A69C-9A97880C9911}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEC2031C-FFB3-4074-9513-9896DAD6DD1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B377DEF2-0EAA-43AD-A785-CDCEBF29A2B4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AE42273-4C11-4D3A-95B0-D6B50E30E8BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5A2518D-BBAE-4236-B65B-55B09DBB6877}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D914FE5A-C7A1-4BB0-A69C-9A97880C9911}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA17C316-7B35-4EA1-B088-ECBE884E933B}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B377DEF2-0EAA-43AD-A785-CDCEBF29A2B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90DC513B-1111-4F58-A015-3A36BD2388CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5A2518D-BBAE-4236-B65B-55B09DBB6877}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20ECF7DB-66C2-4AA5-8FB0-CB627951618B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA17C316-7B35-4EA1-B088-ECBE884E933B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E59F74B8-4EAA-403D-AA6D-C030B8E0D90F}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90DC513B-1111-4F58-A015-3A36BD2388CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22CA1BD8-F189-4FED-851C-41C18FC3625D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20ECF7DB-66C2-4AA5-8FB0-CB627951618B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59D2AF78-9599-4C5A-9C31-28A3C2008AD3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E59F74B8-4EAA-403D-AA6D-C030B8E0D90F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1200E362-BC61-4A3F-9400-47148521FB95}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22CA1BD8-F189-4FED-851C-41C18FC3625D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54575CE3-32FB-468F-AEE2-1D971CAE46A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59D2AF78-9599-4C5A-9C31-28A3C2008AD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB51A4F4-4C6E-4F9A-9EBD-22512E084D56}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1200E362-BC61-4A3F-9400-47148521FB95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E30976C-1AAB-43E6-984C-D90ABF98798A}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,291 +9770,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54575CE3-32FB-468F-AEE2-1D971CAE46A9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB51A4F4-4C6E-4F9A-9EBD-22512E084D56}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E30976C-1AAB-43E6-984C-D90ABF98798A}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,4 +9770,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8032E005-F206-457F-860F-7DC38D86DB61}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D1DDCA3-8E80-4246-A5D1-E3CC21C4E6C4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0321E8E-4DF4-4664-A2B0-419251617260}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -187,43 +187,223 @@
     <t>16</t>
   </si>
   <si>
+    <t>Aotus nancymaae</t>
+  </si>
+  <si>
+    <t>Aotus_trivirgatus</t>
+  </si>
+  <si>
+    <t>3.15</t>
+  </si>
+  <si>
+    <t>Avahi_laniger</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Mandrillus_sphinx*</t>
+  </si>
+  <si>
+    <t>13.9</t>
+  </si>
+  <si>
+    <t>Avahi_occidentalis</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Papio_hamadryas</t>
+  </si>
+  <si>
+    <t>36.9</t>
+  </si>
+  <si>
+    <t>Callimico_goeldii</t>
+  </si>
+  <si>
+    <t>6.85</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Callithrix_jacchus</t>
+  </si>
+  <si>
+    <t>8.5500000000000007</t>
+  </si>
+  <si>
+    <t>Cheirogaleus_major</t>
+  </si>
+  <si>
+    <t>Cheirogaleus_medius</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Homo_sapiens</t>
+  </si>
+  <si>
+    <t>Daubentonia_madagascariensis</t>
+  </si>
+  <si>
+    <t>Pongo_pygmaeus</t>
+  </si>
+  <si>
     <t>Erythrocebus_patas</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
+    <t>Alouatta_palliata*</t>
+  </si>
+  <si>
+    <t>13.1</t>
+  </si>
+  <si>
+    <t>Alouatta_seniculus</t>
+  </si>
+  <si>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>Ateles_paniscus</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Eulemur_fulvus</t>
+  </si>
+  <si>
+    <t>9.15</t>
+  </si>
+  <si>
+    <t>Callicebus_moloch*</t>
+  </si>
+  <si>
+    <t>2.95</t>
+  </si>
+  <si>
+    <t>Galago_demidoff</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>Galago_senegalensis</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Gorilla_gorilla</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Hylobates_lar</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Indri_indri</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Cebus_albifrons</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Lagothrix_lagothricha</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Tarsius_bancanus</t>
+  </si>
+  <si>
+    <t>Tarsius_syrichta</t>
+  </si>
+  <si>
+    <t>Lepilemur_ruficaudatus</t>
+  </si>
+  <si>
+    <t>Lophocebus_albigena</t>
+  </si>
+  <si>
+    <t>Loris_tardigradus</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Macaca_mulatta</t>
+  </si>
+  <si>
+    <t>38.5</t>
+  </si>
+  <si>
+    <t>Microcebus murinus</t>
+  </si>
+  <si>
+    <t>Microcebus_murinus</t>
+  </si>
+  <si>
     <t>Miopithecus_talapoin</t>
   </si>
   <si>
     <t>91.2</t>
   </si>
   <si>
-    <t>Mandrillus_sphinx*</t>
-  </si>
-  <si>
-    <t>13.9</t>
-  </si>
-  <si>
-    <t>Lophocebus_albigena</t>
-  </si>
-  <si>
-    <t>Papio anubis</t>
-  </si>
-  <si>
-    <t>Papio_hamadryas</t>
-  </si>
-  <si>
-    <t>36.9</t>
-  </si>
-  <si>
-    <t>Macaca mulatta</t>
-  </si>
-  <si>
-    <t>Macaca_mulatta</t>
-  </si>
-  <si>
-    <t>38.5</t>
+    <t>Nycticebus_coucang</t>
+  </si>
+  <si>
+    <t>Otolemur garnettii</t>
+  </si>
+  <si>
+    <t>Otolemur_crassicaudatus</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Pan_troglodytes</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Eulemur_mongoz</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>Lemur_catta</t>
+  </si>
+  <si>
+    <t>16.45</t>
+  </si>
+  <si>
+    <t>Perodicticus_potto</t>
   </si>
   <si>
     <t>Piliocolobus_badius</t>
@@ -232,99 +412,18 @@
     <t>&gt;10</t>
   </si>
   <si>
+    <t>Propithecus_verreauxi</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
     <t>Pygathrix_nemaeus</t>
   </si>
   <si>
     <t>9.3000000000000007</t>
   </si>
   <si>
-    <t>Gorilla gorilla gorilla</t>
-  </si>
-  <si>
-    <t>Gorilla_gorilla</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Homo sapiens</t>
-  </si>
-  <si>
-    <t>Homo_sapiens</t>
-  </si>
-  <si>
-    <t>Pan troglodytes</t>
-  </si>
-  <si>
-    <t>Pan_troglodytes</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>Pongo_pygmaeus</t>
-  </si>
-  <si>
-    <t>Hylobates_lar</t>
-  </si>
-  <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>Alouatta_palliata*</t>
-  </si>
-  <si>
-    <t>13.1</t>
-  </si>
-  <si>
-    <t>Alouatta_seniculus</t>
-  </si>
-  <si>
-    <t>7.9</t>
-  </si>
-  <si>
-    <t>Ateles_paniscus</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Lagothrix_lagothricha</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Callicebus_moloch*</t>
-  </si>
-  <si>
-    <t>2.95</t>
-  </si>
-  <si>
-    <t>Aotus nancymaae</t>
-  </si>
-  <si>
-    <t>Aotus_trivirgatus</t>
-  </si>
-  <si>
-    <t>3.15</t>
-  </si>
-  <si>
-    <t>Callimico_goeldii</t>
-  </si>
-  <si>
-    <t>6.85</t>
-  </si>
-  <si>
-    <t>Callithrix jacchus</t>
-  </si>
-  <si>
-    <t>Callithrix_jacchus</t>
-  </si>
-  <si>
-    <t>8.5500000000000007</t>
-  </si>
-  <si>
     <t>Saguinus_midas</t>
   </si>
   <si>
@@ -337,12 +436,6 @@
     <t>7.05</t>
   </si>
   <si>
-    <t>Cebus_albifrons</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>Saimiri boliviensis boliviensis</t>
   </si>
   <si>
@@ -352,103 +445,10 @@
     <t>36.090000000000003</t>
   </si>
   <si>
-    <t>Tarsius_bancanus</t>
-  </si>
-  <si>
-    <t>Tarsius_syrichta</t>
-  </si>
-  <si>
-    <t>Microcebus murinus</t>
-  </si>
-  <si>
-    <t>Microcebus_murinus</t>
-  </si>
-  <si>
-    <t>Cheirogaleus_major</t>
-  </si>
-  <si>
-    <t>Cheirogaleus_medius</t>
-  </si>
-  <si>
-    <t>Avahi_laniger</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Avahi_occidentalis</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Propithecus_verreauxi</t>
-  </si>
-  <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>Indri_indri</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>Daubentonia_madagascariensis</t>
-  </si>
-  <si>
-    <t>Eulemur_fulvus</t>
-  </si>
-  <si>
-    <t>9.15</t>
-  </si>
-  <si>
-    <t>Eulemur_mongoz</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>Lemur_catta</t>
-  </si>
-  <si>
-    <t>16.45</t>
-  </si>
-  <si>
     <t>Varecia_variegata</t>
   </si>
   <si>
     <t>2.8</t>
-  </si>
-  <si>
-    <t>Lepilemur_ruficaudatus</t>
-  </si>
-  <si>
-    <t>Perodicticus_potto</t>
-  </si>
-  <si>
-    <t>Loris_tardigradus</t>
-  </si>
-  <si>
-    <t>Nycticebus_coucang</t>
-  </si>
-  <si>
-    <t>Galago_senegalensis</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>Otolemur garnettii</t>
-  </si>
-  <si>
-    <t>Otolemur_crassicaudatus</t>
-  </si>
-  <si>
-    <t>Galago_demidoff</t>
-  </si>
-  <si>
-    <t>5.5</t>
   </si>
   <si>
     <t>Cynocephalus_volans*</t>
@@ -1880,201 +1880,198 @@
       </c>
     </row>
     <row r="11" spans="1:41">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11">
-        <v>7421.4</v>
+        <v>783.6</v>
       </c>
       <c r="D11">
-        <v>105.65</v>
+        <v>17.4</v>
+      </c>
+      <c r="E11">
+        <v>10.1</v>
       </c>
       <c r="F11">
-        <v>77141</v>
+        <v>9950</v>
       </c>
       <c r="G11">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="H11">
-        <v>561</v>
+        <v>105</v>
       </c>
       <c r="I11">
-        <v>21.6</v>
+        <v>25.25</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>28.56666667</v>
       </c>
       <c r="K11">
-        <v>1095</v>
+        <v>868.9027779</v>
       </c>
       <c r="L11">
-        <v>1246.07</v>
+        <v>821</v>
       </c>
       <c r="M11">
-        <v>1246.07</v>
+        <v>730</v>
       </c>
       <c r="N11">
-        <v>167</v>
+        <v>137.5</v>
       </c>
       <c r="O11">
         <v>1</v>
       </c>
+      <c r="P11">
+        <v>1.4</v>
+      </c>
       <c r="Q11">
-        <v>365</v>
+        <v>269</v>
       </c>
       <c r="R11">
-        <v>234</v>
+        <v>110.3333333</v>
       </c>
       <c r="S11">
-        <v>546.5</v>
+        <v>91.25</v>
       </c>
       <c r="T11">
-        <v>1950</v>
+        <v>360</v>
       </c>
       <c r="U11">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="V11">
-        <v>861</v>
+        <v>758.5694446</v>
       </c>
       <c r="W11">
-        <v>2824</v>
+        <v>8.5</v>
       </c>
       <c r="X11">
-        <v>75</v>
+        <v>45.5</v>
       </c>
       <c r="Y11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA11">
         <v>2</v>
       </c>
-      <c r="AB11">
-        <v>20.5</v>
-      </c>
       <c r="AC11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AD11">
-        <v>665</v>
+        <v>357.99</v>
       </c>
       <c r="AF11">
         <v>2</v>
       </c>
+      <c r="AG11">
+        <v>459.45</v>
+      </c>
+      <c r="AI11">
+        <v>1</v>
+      </c>
       <c r="AJ11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK11">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="AL11">
-        <v>416869</v>
+        <v>410950</v>
       </c>
       <c r="AM11">
-        <v>154882</v>
+        <v>59930</v>
       </c>
       <c r="AO11">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:41">
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12">
-        <v>1381</v>
+        <v>1200.1428</v>
       </c>
       <c r="D12">
-        <v>39.1</v>
+        <v>10.6475</v>
       </c>
       <c r="F12">
-        <v>26427</v>
+        <v>4813</v>
       </c>
       <c r="G12">
-        <v>1.74</v>
+        <v>1.255</v>
       </c>
       <c r="H12">
-        <v>262</v>
+        <v>172</v>
       </c>
       <c r="J12">
-        <v>52.56</v>
+        <v>30.9</v>
       </c>
       <c r="K12">
-        <v>1598.7</v>
-      </c>
-      <c r="L12">
-        <v>1395</v>
-      </c>
-      <c r="M12">
-        <v>2008</v>
+        <v>939.875</v>
       </c>
       <c r="N12">
-        <v>164.5</v>
+        <v>135</v>
       </c>
       <c r="O12">
         <v>1</v>
       </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
       <c r="Q12">
-        <v>730.5</v>
+        <v>365</v>
       </c>
       <c r="R12">
-        <v>168.3333333</v>
+        <v>165</v>
       </c>
       <c r="S12">
-        <v>187.1</v>
+        <v>29</v>
       </c>
       <c r="T12">
-        <v>450</v>
-      </c>
-      <c r="U12">
-        <v>3.44</v>
+        <v>500</v>
       </c>
       <c r="V12">
-        <v>1430.366667</v>
+        <v>774.875</v>
       </c>
       <c r="W12">
-        <v>120</v>
+        <v>1.5</v>
       </c>
       <c r="Y12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z12">
         <v>3</v>
       </c>
       <c r="AA12">
-        <v>2</v>
-      </c>
-      <c r="AB12">
-        <v>66.5</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD12">
-        <v>354.99</v>
+        <v>275</v>
       </c>
       <c r="AF12">
         <v>2</v>
       </c>
       <c r="AI12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO12">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:41">
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13">
         <v>12125</v>
@@ -2140,7 +2137,7 @@
         <v>30</v>
       </c>
       <c r="AC13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AD13">
         <v>758.9400000000001</v>
@@ -2166,82 +2163,43 @@
     </row>
     <row r="14" spans="1:41">
       <c r="B14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14">
-        <v>7992.75</v>
+        <v>832.333</v>
       </c>
       <c r="D14">
-        <v>103.375</v>
+        <v>9.685</v>
       </c>
       <c r="F14">
-        <v>68733</v>
+        <v>4443</v>
       </c>
       <c r="G14">
-        <v>1.865</v>
+        <v>1.145</v>
       </c>
       <c r="H14">
-        <v>742</v>
-      </c>
-      <c r="I14">
-        <v>32.7</v>
-      </c>
-      <c r="J14">
-        <v>49.05</v>
-      </c>
-      <c r="K14">
-        <v>1491.9375</v>
-      </c>
-      <c r="L14">
-        <v>2525.48</v>
-      </c>
-      <c r="M14">
-        <v>2525.48</v>
+        <v>73.7</v>
       </c>
       <c r="N14">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
-      </c>
-      <c r="R14">
-        <v>365</v>
-      </c>
-      <c r="S14">
-        <v>498.58</v>
-      </c>
-      <c r="T14">
-        <v>2170</v>
-      </c>
-      <c r="U14">
-        <v>2.61</v>
-      </c>
-      <c r="V14">
-        <v>1126.9375</v>
+        <v>1</v>
       </c>
       <c r="W14">
-        <v>410</v>
-      </c>
-      <c r="X14">
-        <v>64</v>
+        <v>1.5</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA14">
-        <v>2</v>
-      </c>
-      <c r="AB14">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD14">
-        <v>521.55</v>
+        <v>65</v>
       </c>
       <c r="AF14">
         <v>2</v>
@@ -2249,16 +2207,19 @@
       <c r="AI14">
         <v>1</v>
       </c>
+      <c r="AJ14">
+        <v>2</v>
+      </c>
       <c r="AO14">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:41">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>16000</v>
@@ -2327,7 +2288,7 @@
         <v>54</v>
       </c>
       <c r="AC15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AD15">
         <v>675</v>
@@ -2346,210 +2307,237 @@
       </c>
     </row>
     <row r="16" spans="1:41">
-      <c r="A16" t="s">
-        <v>67</v>
-      </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16">
-        <v>7102.833333</v>
+        <v>492.2</v>
       </c>
       <c r="D16">
-        <v>89.22</v>
+        <v>10.95</v>
       </c>
       <c r="E16">
+        <v>5.8</v>
+      </c>
+      <c r="F16">
+        <v>6476</v>
+      </c>
+      <c r="G16">
+        <v>1.255</v>
+      </c>
+      <c r="H16">
+        <v>47.9</v>
+      </c>
+      <c r="I16">
+        <v>17.9</v>
+      </c>
+      <c r="J16">
+        <v>15.73333333</v>
+      </c>
+      <c r="K16">
+        <v>478.5555555</v>
+      </c>
+      <c r="L16">
+        <v>309.5</v>
+      </c>
+      <c r="M16">
+        <v>395</v>
+      </c>
+      <c r="N16">
+        <v>153</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1.2</v>
+      </c>
+      <c r="Q16">
+        <v>206.6666667</v>
+      </c>
+      <c r="R16">
+        <v>69.25</v>
+      </c>
+      <c r="S16">
+        <v>49.5125</v>
+      </c>
+      <c r="T16">
+        <v>167.5</v>
+      </c>
+      <c r="U16">
+        <v>0.7</v>
+      </c>
+      <c r="V16">
+        <v>409.3055555</v>
+      </c>
+      <c r="W16">
+        <v>45</v>
+      </c>
+      <c r="Y16">
+        <v>3</v>
+      </c>
+      <c r="Z16">
+        <v>2</v>
+      </c>
+      <c r="AA16">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD16">
+        <v>280</v>
+      </c>
+      <c r="AF16">
+        <v>2</v>
+      </c>
+      <c r="AI16">
+        <v>1</v>
+      </c>
+      <c r="AJ16">
+        <v>4</v>
+      </c>
+      <c r="AO16">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41">
+      <c r="A17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17">
+        <v>288.12</v>
+      </c>
+      <c r="D17">
+        <v>7.614285714</v>
+      </c>
+      <c r="E17">
+        <v>3.63</v>
+      </c>
+      <c r="F17">
+        <v>4371</v>
+      </c>
+      <c r="G17">
+        <v>1.17</v>
+      </c>
+      <c r="H17">
+        <v>52</v>
+      </c>
+      <c r="I17">
+        <v>16.75</v>
+      </c>
+      <c r="J17">
+        <v>18.25</v>
+      </c>
+      <c r="K17">
+        <v>555.1041667</v>
+      </c>
+      <c r="L17">
+        <v>421</v>
+      </c>
+      <c r="M17">
+        <v>382</v>
+      </c>
+      <c r="N17">
+        <v>146</v>
+      </c>
+      <c r="O17">
+        <v>2.31</v>
+      </c>
+      <c r="P17">
+        <v>2</v>
+      </c>
+      <c r="Q17">
+        <v>163</v>
+      </c>
+      <c r="R17">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="S17">
+        <v>27.9325</v>
+      </c>
+      <c r="T17">
+        <v>107.785</v>
+      </c>
+      <c r="U17">
+        <v>0.85</v>
+      </c>
+      <c r="V17">
+        <v>484.7041667</v>
+      </c>
+      <c r="W17">
+        <v>6.5</v>
+      </c>
+      <c r="X17">
+        <v>22</v>
+      </c>
+      <c r="Y17">
+        <v>3</v>
+      </c>
+      <c r="Z17">
+        <v>5</v>
+      </c>
+      <c r="AA17">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF17">
+        <v>2</v>
+      </c>
+      <c r="AG17">
+        <v>152</v>
+      </c>
+      <c r="AI17">
+        <v>1</v>
+      </c>
+      <c r="AJ17">
+        <v>2</v>
+      </c>
+      <c r="AN17">
         <v>58</v>
       </c>
-      <c r="F16">
-        <v>63482</v>
-      </c>
-      <c r="G16">
-        <v>1.79</v>
-      </c>
-      <c r="H16">
-        <v>834</v>
-      </c>
-      <c r="I16">
-        <v>36</v>
-      </c>
-      <c r="J16">
-        <v>50</v>
-      </c>
-      <c r="K16">
-        <v>1520.833333</v>
-      </c>
-      <c r="L16">
-        <v>1231</v>
-      </c>
-      <c r="M16">
-        <v>2007</v>
-      </c>
-      <c r="N16">
-        <v>165.6666667</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>1</v>
-      </c>
-      <c r="Q16">
-        <v>404.5</v>
-      </c>
-      <c r="R16">
-        <v>292.5</v>
-      </c>
-      <c r="S16">
-        <v>485.825</v>
-      </c>
-      <c r="T16">
-        <v>1435</v>
-      </c>
-      <c r="U16">
-        <v>2.46</v>
-      </c>
-      <c r="V16">
-        <v>1228.333333</v>
-      </c>
-      <c r="W16">
-        <v>400</v>
-      </c>
-      <c r="X16">
-        <v>63</v>
-      </c>
-      <c r="Y16">
-        <v>3</v>
-      </c>
-      <c r="Z16">
-        <v>1</v>
-      </c>
-      <c r="AA16">
-        <v>2</v>
-      </c>
-      <c r="AB16">
-        <v>48</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD16">
-        <v>555</v>
-      </c>
-      <c r="AF16">
-        <v>2</v>
-      </c>
-      <c r="AG16">
-        <v>2239</v>
-      </c>
-      <c r="AJ16">
-        <v>3</v>
-      </c>
-      <c r="AK16">
-        <v>0.27</v>
-      </c>
-      <c r="AL16">
-        <v>422149</v>
-      </c>
-      <c r="AM16">
-        <v>113783</v>
-      </c>
-      <c r="AN16">
-        <v>60</v>
-      </c>
-      <c r="AO16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41">
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17">
-        <v>7854.833333</v>
-      </c>
-      <c r="D17">
-        <v>76.75</v>
-      </c>
-      <c r="F17">
-        <v>50906</v>
-      </c>
-      <c r="G17">
-        <v>1.805</v>
-      </c>
-      <c r="H17">
-        <v>455</v>
-      </c>
-      <c r="J17">
-        <v>45.45</v>
-      </c>
-      <c r="K17">
-        <v>1382.4375</v>
-      </c>
-      <c r="R17">
-        <v>656.2</v>
-      </c>
-      <c r="V17">
-        <v>726.2375</v>
-      </c>
-      <c r="W17">
-        <v>71</v>
-      </c>
-      <c r="X17">
-        <v>26</v>
-      </c>
-      <c r="Y17">
-        <v>3</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF17">
-        <v>2</v>
-      </c>
-      <c r="AI17">
-        <v>1</v>
-      </c>
       <c r="AO17">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:41">
       <c r="B18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18">
-        <v>8481.666667</v>
+        <v>433.25</v>
       </c>
       <c r="D18">
-        <v>84.83333333</v>
+        <v>6.433333333</v>
       </c>
       <c r="F18">
-        <v>48763</v>
+        <v>2938</v>
       </c>
       <c r="G18">
-        <v>1.635</v>
+        <v>1.15</v>
       </c>
       <c r="H18">
-        <v>911</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I18">
-        <v>30</v>
-      </c>
-      <c r="J18">
-        <v>48</v>
-      </c>
-      <c r="K18">
-        <v>1460</v>
+        <v>15</v>
       </c>
       <c r="L18">
-        <v>1460</v>
+        <v>365</v>
+      </c>
+      <c r="M18">
+        <v>365</v>
       </c>
       <c r="N18">
-        <v>190.5</v>
+        <v>70</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P18">
         <v>1</v>
@@ -2558,31 +2546,31 @@
         <v>365</v>
       </c>
       <c r="R18">
-        <v>330</v>
+        <v>45</v>
       </c>
       <c r="S18">
-        <v>428.25</v>
-      </c>
-      <c r="V18">
-        <v>1130</v>
+        <v>14.09</v>
+      </c>
+      <c r="W18">
+        <v>4.2</v>
       </c>
       <c r="Y18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB18">
-        <v>9.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="AD18">
-        <v>326.37</v>
+        <v>225</v>
       </c>
       <c r="AF18">
         <v>2</v>
@@ -2590,129 +2578,123 @@
       <c r="AI18">
         <v>1</v>
       </c>
+      <c r="AJ18">
+        <v>1</v>
+      </c>
       <c r="AO18">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:41">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
       <c r="B19" t="s">
         <v>75</v>
       </c>
       <c r="C19">
-        <v>99648.39999999999</v>
+        <v>214</v>
       </c>
       <c r="D19">
-        <v>477.44</v>
-      </c>
-      <c r="E19">
-        <v>227</v>
+        <v>3.013333333</v>
       </c>
       <c r="F19">
-        <v>341444</v>
+        <v>1221</v>
       </c>
       <c r="G19">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="H19">
-        <v>3608</v>
+        <v>24.6</v>
       </c>
       <c r="I19">
-        <v>50</v>
+        <v>19.25</v>
       </c>
       <c r="J19">
-        <v>103.5</v>
+        <v>14.33333333</v>
       </c>
       <c r="K19">
-        <v>3148.125</v>
+        <v>435.9722221</v>
       </c>
       <c r="L19">
-        <v>2829</v>
+        <v>365</v>
       </c>
       <c r="M19">
-        <v>4015</v>
+        <v>730</v>
       </c>
       <c r="N19">
-        <v>264.5</v>
+        <v>61.66666667</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="P19">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>1403.5</v>
+        <v>365</v>
       </c>
       <c r="R19">
-        <v>1004</v>
+        <v>61.5</v>
       </c>
       <c r="S19">
-        <v>1979.25</v>
-      </c>
-      <c r="T19">
-        <v>12595</v>
+        <v>19</v>
       </c>
       <c r="U19">
-        <v>6.58</v>
+        <v>0.86</v>
       </c>
       <c r="V19">
-        <v>2144.125</v>
+        <v>374.4722221</v>
       </c>
       <c r="W19">
-        <v>1800</v>
-      </c>
-      <c r="X19">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="Y19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z19">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AA19">
+        <v>2</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="AD19">
-        <v>1594.44</v>
+        <v>225</v>
       </c>
       <c r="AF19">
         <v>2</v>
       </c>
-      <c r="AH19">
-        <v>5248.98</v>
+      <c r="AG19">
+        <v>148.1</v>
       </c>
       <c r="AI19">
         <v>1</v>
       </c>
       <c r="AJ19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AK19">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="AL19">
-        <v>144544</v>
+        <v>186209</v>
       </c>
       <c r="AM19">
-        <v>138038</v>
+        <v>109648</v>
       </c>
       <c r="AO19">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:41">
       <c r="A20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" t="s">
         <v>77</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
       </c>
       <c r="C20">
         <v>61770.315</v>
@@ -2806,80 +2788,71 @@
       </c>
     </row>
     <row r="21" spans="1:41">
-      <c r="A21" t="s">
-        <v>79</v>
-      </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C21">
-        <v>41057.09091</v>
+        <v>2640.285</v>
       </c>
       <c r="D21">
-        <v>392.06</v>
-      </c>
-      <c r="E21">
-        <v>128</v>
+        <v>44.8875</v>
       </c>
       <c r="F21">
-        <v>291592</v>
+        <v>22127</v>
       </c>
       <c r="G21">
-        <v>2.455</v>
+        <v>1.25</v>
       </c>
       <c r="H21">
-        <v>1899</v>
+        <v>392</v>
       </c>
       <c r="I21">
-        <v>59.4</v>
+        <v>24.25</v>
       </c>
       <c r="J21">
-        <v>164.8</v>
+        <v>35.5</v>
       </c>
       <c r="K21">
-        <v>5012.666667</v>
+        <v>1079.791667</v>
       </c>
       <c r="L21">
-        <v>3376</v>
-      </c>
-      <c r="M21">
-        <v>2920</v>
+        <v>882</v>
       </c>
       <c r="N21">
-        <v>234</v>
+        <v>164.5</v>
       </c>
       <c r="O21">
         <v>1</v>
       </c>
       <c r="P21">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q21">
-        <v>1320</v>
+        <v>756</v>
       </c>
       <c r="R21">
-        <v>1579.5</v>
+        <v>244</v>
       </c>
       <c r="S21">
-        <v>1736.25</v>
+        <v>119.3333333</v>
       </c>
       <c r="T21">
-        <v>8500</v>
+        <v>1535</v>
       </c>
       <c r="U21">
-        <v>8.300000000000001</v>
+        <v>2.04</v>
       </c>
       <c r="V21">
-        <v>3433.166667</v>
+        <v>835.7916667</v>
       </c>
       <c r="W21">
-        <v>1085</v>
+        <v>11</v>
       </c>
       <c r="X21">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z21">
         <v>6</v>
@@ -2888,45 +2861,30 @@
         <v>2</v>
       </c>
       <c r="AB21">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="AD21">
-        <v>796.09</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AF21">
         <v>2</v>
       </c>
       <c r="AG21">
-        <v>9000</v>
+        <v>1393.9</v>
       </c>
       <c r="AI21">
         <v>2</v>
       </c>
-      <c r="AJ21">
-        <v>3</v>
-      </c>
-      <c r="AK21">
-        <v>0.59</v>
-      </c>
-      <c r="AL21">
-        <v>208930</v>
-      </c>
-      <c r="AM21">
-        <v>123027</v>
-      </c>
       <c r="AO21">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:41">
       <c r="B22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C22">
         <v>42447.66667</v>
@@ -3030,73 +2988,67 @@
     </row>
     <row r="23" spans="1:41">
       <c r="B23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C23">
-        <v>5724.857143</v>
+        <v>7421.4</v>
       </c>
       <c r="D23">
-        <v>101.52</v>
-      </c>
-      <c r="E23">
-        <v>65</v>
+        <v>105.65</v>
       </c>
       <c r="F23">
-        <v>65800</v>
+        <v>77141</v>
       </c>
       <c r="G23">
-        <v>1.855</v>
+        <v>1.91</v>
       </c>
       <c r="H23">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="I23">
-        <v>44</v>
+        <v>21.6</v>
       </c>
       <c r="J23">
-        <v>101.1933333</v>
+        <v>36</v>
       </c>
       <c r="K23">
-        <v>3077.963888</v>
+        <v>1095</v>
       </c>
       <c r="L23">
-        <v>2555</v>
+        <v>1246.07</v>
       </c>
       <c r="M23">
-        <v>1825</v>
+        <v>1246.07</v>
       </c>
       <c r="N23">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="O23">
         <v>1</v>
       </c>
-      <c r="P23">
-        <v>0.5</v>
-      </c>
       <c r="Q23">
-        <v>997.5</v>
+        <v>365</v>
       </c>
       <c r="R23">
-        <v>626</v>
+        <v>234</v>
       </c>
       <c r="S23">
-        <v>378.55</v>
+        <v>546.5</v>
       </c>
       <c r="T23">
-        <v>1070</v>
+        <v>1950</v>
       </c>
       <c r="U23">
-        <v>6.73</v>
+        <v>1.96</v>
       </c>
       <c r="V23">
-        <v>2451.963888</v>
+        <v>861</v>
       </c>
       <c r="W23">
-        <v>57</v>
+        <v>2824</v>
       </c>
       <c r="X23">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Y23">
         <v>3</v>
@@ -3107,25 +3059,37 @@
       <c r="AA23">
         <v>2</v>
       </c>
+      <c r="AB23">
+        <v>20.5</v>
+      </c>
       <c r="AC23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AD23">
-        <v>545</v>
+        <v>665</v>
       </c>
       <c r="AF23">
         <v>2</v>
       </c>
       <c r="AJ23">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="AK23">
+        <v>0.37</v>
+      </c>
+      <c r="AL23">
+        <v>416869</v>
+      </c>
+      <c r="AM23">
+        <v>154882</v>
       </c>
       <c r="AO23">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:41">
       <c r="B24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C24">
         <v>5892.8</v>
@@ -3191,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="AC24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AD24">
         <v>576.35</v>
@@ -3223,7 +3187,7 @@
     </row>
     <row r="25" spans="1:41">
       <c r="B25" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C25">
         <v>5889.571429</v>
@@ -3286,7 +3250,7 @@
         <v>2</v>
       </c>
       <c r="AC25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AD25">
         <v>560.21</v>
@@ -3306,7 +3270,7 @@
     </row>
     <row r="26" spans="1:41">
       <c r="B26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C26">
         <v>8447.428571</v>
@@ -3372,7 +3336,7 @@
         <v>2</v>
       </c>
       <c r="AC26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AD26">
         <v>575.96</v>
@@ -3389,70 +3353,70 @@
     </row>
     <row r="27" spans="1:41">
       <c r="B27" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C27">
-        <v>5959</v>
+        <v>1933.8</v>
       </c>
       <c r="D27">
-        <v>95.575</v>
+        <v>28.1</v>
+      </c>
+      <c r="E27">
+        <v>10.69</v>
       </c>
       <c r="F27">
-        <v>65873</v>
+        <v>12207</v>
       </c>
       <c r="G27">
-        <v>1.97</v>
+        <v>1.46</v>
       </c>
       <c r="H27">
-        <v>1090</v>
+        <v>194</v>
       </c>
       <c r="I27">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J27">
-        <v>75.5</v>
+        <v>29.875</v>
       </c>
       <c r="K27">
-        <v>2296.458333</v>
+        <v>908.6979167</v>
       </c>
       <c r="L27">
-        <v>2555</v>
+        <v>548</v>
       </c>
       <c r="M27">
-        <v>1520</v>
+        <v>548</v>
       </c>
       <c r="N27">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="O27">
         <v>1</v>
       </c>
-      <c r="P27">
-        <v>0.5</v>
-      </c>
       <c r="Q27">
-        <v>288</v>
+        <v>730</v>
       </c>
       <c r="R27">
-        <v>391.3333333</v>
+        <v>159</v>
       </c>
       <c r="S27">
-        <v>393</v>
+        <v>75.7</v>
+      </c>
+      <c r="T27">
+        <v>1350</v>
       </c>
       <c r="U27">
-        <v>3.53</v>
+        <v>1.46</v>
       </c>
       <c r="V27">
-        <v>1905.125</v>
+        <v>749.6979167</v>
       </c>
       <c r="W27">
-        <v>400</v>
-      </c>
-      <c r="X27">
-        <v>79</v>
+        <v>8.75</v>
       </c>
       <c r="Y27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z27">
         <v>4</v>
@@ -3460,11 +3424,14 @@
       <c r="AA27">
         <v>2</v>
       </c>
+      <c r="AB27">
+        <v>9.25</v>
+      </c>
       <c r="AC27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AD27">
-        <v>536.39</v>
+        <v>469.62</v>
       </c>
       <c r="AF27">
         <v>2</v>
@@ -3476,12 +3443,12 @@
         <v>3</v>
       </c>
       <c r="AO27">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:41">
       <c r="B28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C28">
         <v>980</v>
@@ -3541,7 +3508,7 @@
         <v>2</v>
       </c>
       <c r="AC28" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AD28">
         <v>358.65</v>
@@ -3569,374 +3536,383 @@
       </c>
     </row>
     <row r="29" spans="1:41">
-      <c r="A29" t="s">
-        <v>95</v>
-      </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C29">
-        <v>783.6</v>
+        <v>71.5</v>
       </c>
       <c r="D29">
-        <v>17.4</v>
+        <v>3.345</v>
       </c>
       <c r="E29">
-        <v>10.1</v>
+        <v>1.199</v>
       </c>
       <c r="F29">
-        <v>9950</v>
+        <v>1568</v>
       </c>
       <c r="G29">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="H29">
-        <v>105</v>
+        <v>30.4</v>
       </c>
       <c r="I29">
-        <v>25.25</v>
+        <v>14</v>
       </c>
       <c r="J29">
-        <v>28.56666667</v>
+        <v>21.4</v>
       </c>
       <c r="K29">
-        <v>868.9027779</v>
+        <v>650.9166667</v>
       </c>
       <c r="L29">
-        <v>821</v>
+        <v>240</v>
       </c>
       <c r="M29">
-        <v>730</v>
+        <v>274</v>
       </c>
       <c r="N29">
-        <v>137.5</v>
+        <v>110.3333333</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="P29">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q29">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="R29">
-        <v>110.3333333</v>
+        <v>45</v>
       </c>
       <c r="S29">
-        <v>91.25</v>
-      </c>
-      <c r="T29">
-        <v>360</v>
-      </c>
-      <c r="U29">
-        <v>1.81</v>
+        <v>8.466666667</v>
       </c>
       <c r="V29">
-        <v>758.5694446</v>
+        <v>605.9166667</v>
       </c>
       <c r="W29">
-        <v>8.5</v>
-      </c>
-      <c r="X29">
-        <v>45.5</v>
+        <v>1</v>
       </c>
       <c r="Y29">
         <v>1</v>
       </c>
       <c r="Z29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA29">
         <v>2</v>
       </c>
       <c r="AC29" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AD29">
-        <v>357.99</v>
+        <v>120</v>
       </c>
       <c r="AF29">
         <v>2</v>
       </c>
       <c r="AG29">
-        <v>459.45</v>
-      </c>
-      <c r="AI29">
-        <v>1</v>
+        <v>59.4</v>
       </c>
       <c r="AJ29">
-        <v>2</v>
-      </c>
-      <c r="AK29">
-        <v>0.12</v>
-      </c>
-      <c r="AL29">
-        <v>410950</v>
-      </c>
-      <c r="AM29">
-        <v>59930</v>
+        <v>4</v>
       </c>
       <c r="AO29">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:41">
       <c r="B30" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C30">
-        <v>492.2</v>
+        <v>178.7</v>
       </c>
       <c r="D30">
-        <v>10.95</v>
+        <v>4.8</v>
       </c>
       <c r="E30">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="F30">
-        <v>6476</v>
+        <v>2139</v>
       </c>
       <c r="G30">
-        <v>1.255</v>
+        <v>1.17</v>
       </c>
       <c r="H30">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="I30">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="J30">
-        <v>15.73333333</v>
+        <v>11.4</v>
       </c>
       <c r="K30">
-        <v>478.5555555</v>
+        <v>346.75</v>
       </c>
       <c r="L30">
-        <v>309.5</v>
+        <v>240</v>
       </c>
       <c r="M30">
-        <v>395</v>
+        <v>300</v>
       </c>
       <c r="N30">
-        <v>153</v>
+        <v>130.6666667</v>
       </c>
       <c r="O30">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="P30">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q30">
-        <v>206.6666667</v>
+        <v>242.5</v>
       </c>
       <c r="R30">
-        <v>69.25</v>
+        <v>87.33333333</v>
       </c>
       <c r="S30">
-        <v>49.5125</v>
+        <v>15.55</v>
       </c>
       <c r="T30">
-        <v>167.5</v>
+        <v>125</v>
       </c>
       <c r="U30">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="V30">
-        <v>409.3055555</v>
+        <v>259.4166667</v>
       </c>
       <c r="W30">
-        <v>45</v>
+        <v>11</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA30">
         <v>2</v>
       </c>
       <c r="AC30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AD30">
-        <v>280</v>
+        <v>160</v>
       </c>
       <c r="AF30">
         <v>2</v>
       </c>
-      <c r="AI30">
-        <v>1</v>
+      <c r="AG30">
+        <v>180.225</v>
       </c>
       <c r="AJ30">
         <v>4</v>
       </c>
+      <c r="AK30">
+        <v>0.45</v>
+      </c>
+      <c r="AL30">
+        <v>338844</v>
+      </c>
+      <c r="AM30">
+        <v>151356</v>
+      </c>
       <c r="AO30">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:41">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C31">
-        <v>288.12</v>
+        <v>99648.39999999999</v>
       </c>
       <c r="D31">
-        <v>7.614285714</v>
+        <v>477.44</v>
       </c>
       <c r="E31">
-        <v>3.63</v>
+        <v>227</v>
       </c>
       <c r="F31">
-        <v>4371</v>
+        <v>341444</v>
       </c>
       <c r="G31">
-        <v>1.17</v>
+        <v>2.26</v>
       </c>
       <c r="H31">
-        <v>52</v>
+        <v>3608</v>
       </c>
       <c r="I31">
-        <v>16.75</v>
+        <v>50</v>
       </c>
       <c r="J31">
-        <v>18.25</v>
+        <v>103.5</v>
       </c>
       <c r="K31">
-        <v>555.1041667</v>
+        <v>3148.125</v>
       </c>
       <c r="L31">
-        <v>421</v>
+        <v>2829</v>
       </c>
       <c r="M31">
-        <v>382</v>
+        <v>4015</v>
       </c>
       <c r="N31">
-        <v>146</v>
+        <v>264.5</v>
       </c>
       <c r="O31">
-        <v>2.31</v>
+        <v>1</v>
       </c>
       <c r="P31">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="Q31">
-        <v>163</v>
+        <v>1403.5</v>
       </c>
       <c r="R31">
-        <v>70.40000000000001</v>
+        <v>1004</v>
       </c>
       <c r="S31">
-        <v>27.9325</v>
+        <v>1979.25</v>
       </c>
       <c r="T31">
-        <v>107.785</v>
+        <v>12595</v>
       </c>
       <c r="U31">
-        <v>0.85</v>
+        <v>6.58</v>
       </c>
       <c r="V31">
-        <v>484.7041667</v>
+        <v>2144.125</v>
       </c>
       <c r="W31">
-        <v>6.5</v>
+        <v>1800</v>
       </c>
       <c r="X31">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="Y31">
         <v>3</v>
       </c>
       <c r="Z31">
-        <v>5</v>
-      </c>
-      <c r="AA31">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="AB31">
+        <v>10</v>
       </c>
       <c r="AC31" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="AD31">
+        <v>1594.44</v>
       </c>
       <c r="AF31">
         <v>2</v>
       </c>
-      <c r="AG31">
-        <v>152</v>
+      <c r="AH31">
+        <v>5248.98</v>
       </c>
       <c r="AI31">
         <v>1</v>
       </c>
       <c r="AJ31">
-        <v>2</v>
-      </c>
-      <c r="AN31">
-        <v>58</v>
+        <v>4</v>
+      </c>
+      <c r="AK31">
+        <v>0.95</v>
+      </c>
+      <c r="AL31">
+        <v>144544</v>
+      </c>
+      <c r="AM31">
+        <v>138038</v>
       </c>
       <c r="AO31">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:41">
       <c r="B32" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C32">
-        <v>439.2</v>
+        <v>5724.857143</v>
       </c>
       <c r="D32">
-        <v>10.5</v>
+        <v>101.52</v>
+      </c>
+      <c r="E32">
+        <v>65</v>
       </c>
       <c r="F32">
-        <v>5883</v>
+        <v>65800</v>
       </c>
       <c r="G32">
-        <v>1.195</v>
+        <v>1.855</v>
       </c>
       <c r="H32">
-        <v>251</v>
+        <v>555</v>
       </c>
       <c r="I32">
-        <v>13.3</v>
+        <v>44</v>
       </c>
       <c r="J32">
-        <v>24</v>
+        <v>101.1933333</v>
       </c>
       <c r="K32">
-        <v>730</v>
+        <v>3077.963888</v>
       </c>
       <c r="L32">
-        <v>608</v>
+        <v>2555</v>
+      </c>
+      <c r="M32">
+        <v>1825</v>
       </c>
       <c r="N32">
-        <v>140.5</v>
+        <v>212</v>
       </c>
       <c r="O32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="Q32">
-        <v>240</v>
+        <v>997.5</v>
       </c>
       <c r="R32">
-        <v>70.5</v>
+        <v>626</v>
       </c>
       <c r="S32">
-        <v>38</v>
+        <v>378.55</v>
+      </c>
+      <c r="T32">
+        <v>1070</v>
+      </c>
+      <c r="U32">
+        <v>6.73</v>
       </c>
       <c r="V32">
-        <v>659.5</v>
+        <v>2451.963888</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="X32">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="Y32">
         <v>3</v>
@@ -3948,75 +3924,81 @@
         <v>2</v>
       </c>
       <c r="AC32" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="AD32">
-        <v>264.21</v>
+        <v>545</v>
       </c>
       <c r="AF32">
         <v>2</v>
       </c>
+      <c r="AJ32">
+        <v>2</v>
+      </c>
       <c r="AO32">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:41">
       <c r="B33" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C33">
-        <v>368.8333333</v>
+        <v>7410.8333</v>
       </c>
       <c r="D33">
-        <v>9.800000000000001</v>
+        <v>37.35</v>
       </c>
       <c r="F33">
-        <v>5894</v>
+        <v>20114</v>
       </c>
       <c r="G33">
-        <v>1.195</v>
+        <v>1.455</v>
+      </c>
+      <c r="H33">
+        <v>330</v>
       </c>
       <c r="I33">
-        <v>23.08</v>
+        <v>34.5</v>
       </c>
       <c r="J33">
-        <v>22.8</v>
+        <v>84</v>
       </c>
       <c r="K33">
-        <v>693.5</v>
+        <v>2555</v>
       </c>
       <c r="L33">
-        <v>548</v>
+        <v>2008</v>
       </c>
       <c r="M33">
-        <v>550</v>
+        <v>2008</v>
       </c>
       <c r="N33">
-        <v>161.5</v>
+        <v>159.5</v>
       </c>
       <c r="O33">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="P33">
-        <v>1</v>
+        <v>0.42</v>
       </c>
       <c r="Q33">
-        <v>262</v>
+        <v>906</v>
       </c>
       <c r="R33">
-        <v>52</v>
+        <v>364.3333333</v>
       </c>
       <c r="S33">
-        <v>41.28</v>
-      </c>
-      <c r="T33">
-        <v>105</v>
+        <v>300</v>
       </c>
       <c r="V33">
-        <v>641.5</v>
+        <v>2190.666667</v>
       </c>
       <c r="W33">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="X33">
+        <v>43</v>
       </c>
       <c r="Y33">
         <v>3</v>
@@ -4025,13 +4007,16 @@
         <v>4</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AB33">
+        <v>3.5</v>
       </c>
       <c r="AC33" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AD33">
-        <v>239.99</v>
+        <v>734.99</v>
       </c>
       <c r="AF33">
         <v>2</v>
@@ -4039,25 +4024,13 @@
       <c r="AI33">
         <v>1</v>
       </c>
-      <c r="AJ33">
-        <v>2</v>
-      </c>
-      <c r="AK33">
-        <v>0.3</v>
-      </c>
-      <c r="AL33">
-        <v>328541</v>
-      </c>
-      <c r="AM33">
-        <v>102329</v>
-      </c>
       <c r="AO33">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:41">
       <c r="B34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C34">
         <v>2482.8</v>
@@ -4129,7 +4102,7 @@
         <v>2</v>
       </c>
       <c r="AC34" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AD34">
         <v>384.28</v>
@@ -4148,118 +4121,100 @@
       </c>
     </row>
     <row r="35" spans="1:41">
-      <c r="A35" t="s">
-        <v>109</v>
-      </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C35">
-        <v>680.6</v>
+        <v>5959</v>
       </c>
       <c r="D35">
-        <v>22.98</v>
-      </c>
-      <c r="E35">
-        <v>15.24</v>
+        <v>95.575</v>
       </c>
       <c r="F35">
-        <v>15541</v>
+        <v>65873</v>
       </c>
       <c r="G35">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="H35">
-        <v>299</v>
+        <v>1090</v>
       </c>
       <c r="I35">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J35">
-        <v>30</v>
+        <v>75.5</v>
       </c>
       <c r="K35">
-        <v>912.5</v>
+        <v>2296.458333</v>
       </c>
       <c r="L35">
-        <v>1003</v>
+        <v>2555</v>
       </c>
       <c r="M35">
-        <v>1826</v>
+        <v>1520</v>
       </c>
       <c r="N35">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q35">
-        <v>351</v>
+        <v>288</v>
       </c>
       <c r="R35">
-        <v>176</v>
+        <v>391.3333333</v>
       </c>
       <c r="S35">
-        <v>138.6</v>
-      </c>
-      <c r="T35">
-        <v>410.5</v>
+        <v>393</v>
+      </c>
+      <c r="U35">
+        <v>3.53</v>
       </c>
       <c r="V35">
-        <v>736.5</v>
+        <v>1905.125</v>
       </c>
       <c r="W35">
-        <v>157</v>
+        <v>400</v>
       </c>
       <c r="X35">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="Y35">
         <v>3</v>
       </c>
       <c r="Z35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA35">
         <v>2</v>
       </c>
       <c r="AC35" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="AD35">
-        <v>322</v>
+        <v>536.39</v>
       </c>
       <c r="AF35">
         <v>2</v>
       </c>
-      <c r="AG35">
-        <v>738.8099999999999</v>
-      </c>
       <c r="AI35">
         <v>1</v>
       </c>
       <c r="AJ35">
         <v>3</v>
       </c>
-      <c r="AK35">
-        <v>0.25</v>
-      </c>
-      <c r="AL35">
-        <v>478630</v>
-      </c>
-      <c r="AM35">
-        <v>117490</v>
-      </c>
       <c r="AO35">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:41">
       <c r="B36" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C36">
         <v>115.875</v>
@@ -4345,7 +4300,7 @@
     </row>
     <row r="37" spans="1:41">
       <c r="B37" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C37">
         <v>112.05</v>
@@ -4427,181 +4382,157 @@
       </c>
     </row>
     <row r="38" spans="1:41">
-      <c r="A38" t="s">
-        <v>114</v>
-      </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C38">
-        <v>71.828</v>
+        <v>821.8933</v>
       </c>
       <c r="D38">
-        <v>1.846666667</v>
+        <v>7.5</v>
       </c>
       <c r="F38">
-        <v>740</v>
+        <v>3282</v>
       </c>
       <c r="G38">
-        <v>1.1</v>
+        <v>1.135</v>
       </c>
       <c r="H38">
-        <v>11.3</v>
-      </c>
-      <c r="I38">
-        <v>15.5</v>
+        <v>76.5</v>
       </c>
       <c r="J38">
-        <v>14.83333333</v>
+        <v>19.5</v>
       </c>
       <c r="K38">
-        <v>451.1805555</v>
+        <v>593.125</v>
       </c>
       <c r="L38">
-        <v>243</v>
-      </c>
-      <c r="M38">
-        <v>243</v>
+        <v>595</v>
       </c>
       <c r="N38">
-        <v>60.75</v>
+        <v>163</v>
       </c>
       <c r="O38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38">
         <v>1</v>
       </c>
       <c r="Q38">
+        <v>365</v>
+      </c>
+      <c r="R38">
+        <v>121</v>
+      </c>
+      <c r="S38">
+        <v>27</v>
+      </c>
+      <c r="T38">
         <v>250</v>
       </c>
-      <c r="R38">
-        <v>39</v>
-      </c>
-      <c r="S38">
-        <v>5.525</v>
-      </c>
-      <c r="U38">
-        <v>0.73</v>
-      </c>
       <c r="V38">
-        <v>412.1805555</v>
-      </c>
-      <c r="W38">
-        <v>2</v>
-      </c>
-      <c r="X38">
-        <v>51</v>
+        <v>472.125</v>
       </c>
       <c r="Y38">
         <v>1</v>
       </c>
       <c r="Z38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA38">
-        <v>2</v>
-      </c>
-      <c r="AB38">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="AC38" t="s">
         <v>42</v>
       </c>
-      <c r="AD38">
-        <v>143.61</v>
-      </c>
       <c r="AF38">
         <v>2</v>
       </c>
-      <c r="AG38">
-        <v>84.06999999999999</v>
-      </c>
       <c r="AI38">
         <v>1</v>
       </c>
-      <c r="AJ38">
-        <v>1</v>
-      </c>
-      <c r="AK38">
-        <v>0.59</v>
-      </c>
-      <c r="AL38">
-        <v>190546</v>
-      </c>
-      <c r="AM38">
-        <v>112202</v>
-      </c>
       <c r="AO38">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:41">
       <c r="B39" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C39">
-        <v>433.25</v>
+        <v>7992.75</v>
       </c>
       <c r="D39">
-        <v>6.433333333</v>
+        <v>103.375</v>
       </c>
       <c r="F39">
-        <v>2938</v>
+        <v>68733</v>
       </c>
       <c r="G39">
-        <v>1.15</v>
+        <v>1.865</v>
       </c>
       <c r="H39">
-        <v>83.40000000000001</v>
+        <v>742</v>
       </c>
       <c r="I39">
-        <v>15</v>
+        <v>32.7</v>
+      </c>
+      <c r="J39">
+        <v>49.05</v>
+      </c>
+      <c r="K39">
+        <v>1491.9375</v>
       </c>
       <c r="L39">
+        <v>2525.48</v>
+      </c>
+      <c r="M39">
+        <v>2525.48</v>
+      </c>
+      <c r="N39">
+        <v>175</v>
+      </c>
+      <c r="O39">
+        <v>1.01</v>
+      </c>
+      <c r="R39">
         <v>365</v>
       </c>
-      <c r="M39">
-        <v>365</v>
-      </c>
-      <c r="N39">
-        <v>70</v>
-      </c>
-      <c r="O39">
-        <v>2.5</v>
-      </c>
-      <c r="P39">
-        <v>1</v>
-      </c>
-      <c r="Q39">
-        <v>365</v>
-      </c>
-      <c r="R39">
-        <v>45</v>
-      </c>
       <c r="S39">
-        <v>14.09</v>
+        <v>498.58</v>
+      </c>
+      <c r="T39">
+        <v>2170</v>
+      </c>
+      <c r="U39">
+        <v>2.61</v>
+      </c>
+      <c r="V39">
+        <v>1126.9375</v>
       </c>
       <c r="W39">
-        <v>4.2</v>
+        <v>410</v>
+      </c>
+      <c r="X39">
+        <v>64</v>
       </c>
       <c r="Y39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA39">
         <v>2</v>
       </c>
       <c r="AB39">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AC39" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AD39">
-        <v>225</v>
+        <v>521.55</v>
       </c>
       <c r="AF39">
         <v>2</v>
@@ -4609,283 +4540,370 @@
       <c r="AI39">
         <v>1</v>
       </c>
-      <c r="AJ39">
-        <v>1</v>
-      </c>
       <c r="AO39">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:41">
       <c r="B40" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C40">
-        <v>214</v>
+        <v>281.44</v>
       </c>
       <c r="D40">
-        <v>3.013333333</v>
+        <v>6.633333333</v>
+      </c>
+      <c r="E40">
+        <v>2.69</v>
       </c>
       <c r="F40">
-        <v>1221</v>
+        <v>3524</v>
       </c>
       <c r="G40">
-        <v>1.11</v>
+        <v>1.285</v>
       </c>
       <c r="H40">
-        <v>24.6</v>
+        <v>51.6</v>
       </c>
       <c r="I40">
-        <v>19.25</v>
+        <v>16.4</v>
       </c>
       <c r="J40">
-        <v>14.33333333</v>
+        <v>18</v>
       </c>
       <c r="K40">
-        <v>435.9722221</v>
+        <v>547.5</v>
       </c>
       <c r="L40">
+        <v>380</v>
+      </c>
+      <c r="M40">
         <v>365</v>
       </c>
-      <c r="M40">
-        <v>730</v>
-      </c>
       <c r="N40">
-        <v>61.66666667</v>
+        <v>165.75</v>
       </c>
       <c r="O40">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="P40">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q40">
-        <v>365</v>
+        <v>234</v>
       </c>
       <c r="R40">
-        <v>61.5</v>
+        <v>160</v>
       </c>
       <c r="S40">
-        <v>19</v>
+        <v>11.175</v>
+      </c>
+      <c r="T40">
+        <v>139</v>
       </c>
       <c r="U40">
-        <v>0.86</v>
+        <v>0.58</v>
       </c>
       <c r="V40">
-        <v>374.4722221</v>
+        <v>387.5</v>
       </c>
       <c r="W40">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>15</v>
+      </c>
+      <c r="Y40">
+        <v>1</v>
+      </c>
+      <c r="Z40">
         <v>4</v>
       </c>
-      <c r="Y40">
-        <v>1</v>
-      </c>
-      <c r="Z40">
-        <v>5</v>
-      </c>
       <c r="AA40">
         <v>2</v>
-      </c>
-      <c r="AB40">
-        <v>1</v>
       </c>
       <c r="AC40" t="s">
         <v>42</v>
       </c>
       <c r="AD40">
-        <v>225</v>
+        <v>224.49</v>
       </c>
       <c r="AF40">
         <v>2</v>
       </c>
       <c r="AG40">
-        <v>148.1</v>
+        <v>147.5</v>
       </c>
       <c r="AI40">
         <v>1</v>
       </c>
       <c r="AJ40">
-        <v>1</v>
-      </c>
-      <c r="AK40">
+        <v>4</v>
+      </c>
+      <c r="AO40">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:41">
+      <c r="A41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41">
+        <v>7102.833333</v>
+      </c>
+      <c r="D41">
+        <v>89.22</v>
+      </c>
+      <c r="E41">
+        <v>58</v>
+      </c>
+      <c r="F41">
+        <v>63482</v>
+      </c>
+      <c r="G41">
+        <v>1.79</v>
+      </c>
+      <c r="H41">
+        <v>834</v>
+      </c>
+      <c r="I41">
+        <v>36</v>
+      </c>
+      <c r="J41">
+        <v>50</v>
+      </c>
+      <c r="K41">
+        <v>1520.833333</v>
+      </c>
+      <c r="L41">
+        <v>1231</v>
+      </c>
+      <c r="M41">
+        <v>2007</v>
+      </c>
+      <c r="N41">
+        <v>165.6666667</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41">
+        <v>1</v>
+      </c>
+      <c r="Q41">
+        <v>404.5</v>
+      </c>
+      <c r="R41">
+        <v>292.5</v>
+      </c>
+      <c r="S41">
+        <v>485.825</v>
+      </c>
+      <c r="T41">
+        <v>1435</v>
+      </c>
+      <c r="U41">
+        <v>2.46</v>
+      </c>
+      <c r="V41">
+        <v>1228.333333</v>
+      </c>
+      <c r="W41">
+        <v>400</v>
+      </c>
+      <c r="X41">
+        <v>63</v>
+      </c>
+      <c r="Y41">
+        <v>3</v>
+      </c>
+      <c r="Z41">
+        <v>1</v>
+      </c>
+      <c r="AA41">
+        <v>2</v>
+      </c>
+      <c r="AB41">
+        <v>48</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD41">
+        <v>555</v>
+      </c>
+      <c r="AF41">
+        <v>2</v>
+      </c>
+      <c r="AG41">
+        <v>2239</v>
+      </c>
+      <c r="AJ41">
+        <v>3</v>
+      </c>
+      <c r="AK41">
+        <v>0.27</v>
+      </c>
+      <c r="AL41">
+        <v>422149</v>
+      </c>
+      <c r="AM41">
+        <v>113783</v>
+      </c>
+      <c r="AN41">
+        <v>60</v>
+      </c>
+      <c r="AO41">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:41">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42">
+        <v>71.828</v>
+      </c>
+      <c r="D42">
+        <v>1.846666667</v>
+      </c>
+      <c r="F42">
+        <v>740</v>
+      </c>
+      <c r="G42">
+        <v>1.1</v>
+      </c>
+      <c r="H42">
+        <v>11.3</v>
+      </c>
+      <c r="I42">
+        <v>15.5</v>
+      </c>
+      <c r="J42">
+        <v>14.83333333</v>
+      </c>
+      <c r="K42">
+        <v>451.1805555</v>
+      </c>
+      <c r="L42">
+        <v>243</v>
+      </c>
+      <c r="M42">
+        <v>243</v>
+      </c>
+      <c r="N42">
+        <v>60.75</v>
+      </c>
+      <c r="O42">
+        <v>2</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="Q42">
+        <v>250</v>
+      </c>
+      <c r="R42">
+        <v>39</v>
+      </c>
+      <c r="S42">
+        <v>5.525</v>
+      </c>
+      <c r="U42">
+        <v>0.73</v>
+      </c>
+      <c r="V42">
+        <v>412.1805555</v>
+      </c>
+      <c r="W42">
+        <v>2</v>
+      </c>
+      <c r="X42">
+        <v>51</v>
+      </c>
+      <c r="Y42">
+        <v>1</v>
+      </c>
+      <c r="Z42">
+        <v>5</v>
+      </c>
+      <c r="AA42">
+        <v>2</v>
+      </c>
+      <c r="AB42">
+        <v>3.5</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD42">
+        <v>143.61</v>
+      </c>
+      <c r="AF42">
+        <v>2</v>
+      </c>
+      <c r="AG42">
+        <v>84.06999999999999</v>
+      </c>
+      <c r="AI42">
+        <v>1</v>
+      </c>
+      <c r="AJ42">
+        <v>1</v>
+      </c>
+      <c r="AK42">
         <v>0.59</v>
       </c>
-      <c r="AL40">
-        <v>186209</v>
-      </c>
-      <c r="AM40">
-        <v>109648</v>
-      </c>
-      <c r="AO40">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:41">
-      <c r="B41" t="s">
-        <v>118</v>
-      </c>
-      <c r="C41">
-        <v>1200.1428</v>
-      </c>
-      <c r="D41">
-        <v>10.6475</v>
-      </c>
-      <c r="F41">
-        <v>4813</v>
-      </c>
-      <c r="G41">
-        <v>1.255</v>
-      </c>
-      <c r="H41">
-        <v>172</v>
-      </c>
-      <c r="J41">
-        <v>30.9</v>
-      </c>
-      <c r="K41">
-        <v>939.875</v>
-      </c>
-      <c r="N41">
-        <v>135</v>
-      </c>
-      <c r="O41">
-        <v>1</v>
-      </c>
-      <c r="Q41">
-        <v>365</v>
-      </c>
-      <c r="R41">
-        <v>165</v>
-      </c>
-      <c r="S41">
-        <v>29</v>
-      </c>
-      <c r="T41">
-        <v>500</v>
-      </c>
-      <c r="V41">
-        <v>774.875</v>
-      </c>
-      <c r="W41">
-        <v>1.5</v>
-      </c>
-      <c r="Y41">
-        <v>1</v>
-      </c>
-      <c r="Z41">
-        <v>3</v>
-      </c>
-      <c r="AA41">
-        <v>1</v>
-      </c>
-      <c r="AC41" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD41">
-        <v>275</v>
-      </c>
-      <c r="AF41">
-        <v>2</v>
-      </c>
-      <c r="AI41">
-        <v>2</v>
-      </c>
-      <c r="AJ41">
-        <v>2</v>
-      </c>
-      <c r="AO41">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:41">
-      <c r="B42" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42">
-        <v>832.333</v>
-      </c>
-      <c r="D42">
-        <v>9.685</v>
-      </c>
-      <c r="F42">
-        <v>4443</v>
-      </c>
-      <c r="G42">
-        <v>1.145</v>
-      </c>
-      <c r="H42">
-        <v>73.7</v>
-      </c>
-      <c r="N42">
-        <v>135</v>
-      </c>
-      <c r="O42">
-        <v>1</v>
-      </c>
-      <c r="W42">
-        <v>1.5</v>
-      </c>
-      <c r="Y42">
-        <v>2</v>
-      </c>
-      <c r="Z42">
-        <v>1</v>
-      </c>
-      <c r="AA42">
-        <v>1</v>
-      </c>
-      <c r="AC42" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF42">
-        <v>2</v>
-      </c>
-      <c r="AI42">
-        <v>1</v>
-      </c>
-      <c r="AJ42">
-        <v>2</v>
+      <c r="AL42">
+        <v>190546</v>
+      </c>
+      <c r="AM42">
+        <v>112202</v>
       </c>
       <c r="AO42">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:41">
       <c r="B43" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C43">
-        <v>3547.125</v>
+        <v>1381</v>
       </c>
       <c r="D43">
-        <v>26.9</v>
+        <v>39.1</v>
       </c>
       <c r="F43">
-        <v>13170</v>
+        <v>26427</v>
       </c>
       <c r="G43">
-        <v>1.345</v>
+        <v>1.74</v>
       </c>
       <c r="H43">
-        <v>231</v>
-      </c>
-      <c r="I43">
-        <v>20.6</v>
+        <v>262</v>
       </c>
       <c r="J43">
-        <v>43.46666667</v>
+        <v>52.56</v>
       </c>
       <c r="K43">
-        <v>1322.111111</v>
+        <v>1598.7</v>
       </c>
       <c r="L43">
-        <v>912</v>
+        <v>1395</v>
       </c>
       <c r="M43">
-        <v>912</v>
+        <v>2008</v>
       </c>
       <c r="N43">
-        <v>146.75</v>
+        <v>164.5</v>
       </c>
       <c r="O43">
         <v>1</v>
@@ -4894,28 +4912,25 @@
         <v>1</v>
       </c>
       <c r="Q43">
-        <v>448.5</v>
+        <v>730.5</v>
       </c>
       <c r="R43">
-        <v>173.25</v>
+        <v>168.3333333</v>
       </c>
       <c r="S43">
-        <v>94.15000000000001</v>
+        <v>187.1</v>
       </c>
       <c r="T43">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="U43">
-        <v>2.62</v>
+        <v>3.44</v>
       </c>
       <c r="V43">
-        <v>1148.861111</v>
+        <v>1430.366667</v>
       </c>
       <c r="W43">
-        <v>8.5</v>
-      </c>
-      <c r="X43">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="Y43">
         <v>3</v>
@@ -4924,23 +4939,20 @@
         <v>3</v>
       </c>
       <c r="AA43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB43">
-        <v>7.5</v>
+        <v>66.5</v>
       </c>
       <c r="AC43" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="AD43">
-        <v>472.49</v>
+        <v>354.99</v>
       </c>
       <c r="AF43">
         <v>2</v>
       </c>
-      <c r="AG43">
-        <v>670</v>
-      </c>
       <c r="AI43">
         <v>1</v>
       </c>
@@ -4948,291 +4960,339 @@
         <v>3</v>
       </c>
       <c r="AO43">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:41">
       <c r="B44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44">
+        <v>828.1875</v>
+      </c>
+      <c r="D44">
+        <v>11.73333333</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <v>6.192</v>
+      </c>
+      <c r="G44">
+        <v>1.205</v>
+      </c>
+      <c r="H44">
+        <v>142</v>
+      </c>
+      <c r="I44">
+        <v>26.5</v>
+      </c>
+      <c r="J44">
+        <v>25.3</v>
+      </c>
+      <c r="K44">
+        <v>769.5416667</v>
+      </c>
+      <c r="L44">
+        <v>578</v>
+      </c>
+      <c r="N44">
+        <v>192</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="Q44">
+        <v>428.5</v>
+      </c>
+      <c r="R44">
+        <v>157.25</v>
+      </c>
+      <c r="S44">
+        <v>46.16</v>
+      </c>
+      <c r="T44">
+        <v>520</v>
+      </c>
+      <c r="U44">
+        <v>1.09</v>
+      </c>
+      <c r="V44">
+        <v>612.2916667</v>
+      </c>
+      <c r="W44">
+        <v>5</v>
+      </c>
+      <c r="X44">
+        <v>60</v>
+      </c>
+      <c r="Y44">
+        <v>1</v>
+      </c>
+      <c r="Z44">
+        <v>6</v>
+      </c>
+      <c r="AA44">
+        <v>2</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD44">
+        <v>300</v>
+      </c>
+      <c r="AF44">
+        <v>2</v>
+      </c>
+      <c r="AG44">
+        <v>240</v>
+      </c>
+      <c r="AI44">
+        <v>1</v>
+      </c>
+      <c r="AJ44">
+        <v>1</v>
+      </c>
+      <c r="AK44">
+        <v>0.49</v>
+      </c>
+      <c r="AL44">
+        <v>109648</v>
+      </c>
+      <c r="AM44">
+        <v>53703</v>
+      </c>
+      <c r="AO44">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:41">
+      <c r="A45" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45">
+        <v>952.428</v>
+      </c>
+      <c r="D45">
+        <v>10.6</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>4723</v>
+      </c>
+      <c r="G45">
+        <v>1.255</v>
+      </c>
+      <c r="H45">
+        <v>147</v>
+      </c>
+      <c r="I45">
+        <v>15.66</v>
+      </c>
+      <c r="J45">
+        <v>23</v>
+      </c>
+      <c r="K45">
+        <v>699.5833333</v>
+      </c>
+      <c r="L45">
+        <v>430</v>
+      </c>
+      <c r="M45">
+        <v>639</v>
+      </c>
+      <c r="N45">
+        <v>134</v>
+      </c>
+      <c r="O45">
+        <v>1.533333333</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="Q45">
+        <v>281.3333333</v>
+      </c>
+      <c r="R45">
+        <v>121</v>
+      </c>
+      <c r="S45">
+        <v>43.96</v>
+      </c>
+      <c r="T45">
+        <v>500</v>
+      </c>
+      <c r="U45">
+        <v>1.47</v>
+      </c>
+      <c r="V45">
+        <v>578.5833333</v>
+      </c>
+      <c r="W45">
+        <v>10</v>
+      </c>
+      <c r="X45">
+        <v>27</v>
+      </c>
+      <c r="Y45">
+        <v>1</v>
+      </c>
+      <c r="Z45">
+        <v>5</v>
+      </c>
+      <c r="AA45">
+        <v>2</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD45">
+        <v>307</v>
+      </c>
+      <c r="AF45">
+        <v>2</v>
+      </c>
+      <c r="AG45">
+        <v>457.15</v>
+      </c>
+      <c r="AJ45">
+        <v>1</v>
+      </c>
+      <c r="AO45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:41">
+      <c r="A46" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46">
+        <v>41057.09091</v>
+      </c>
+      <c r="D46">
+        <v>392.06</v>
+      </c>
+      <c r="E46">
+        <v>128</v>
+      </c>
+      <c r="F46">
+        <v>291592</v>
+      </c>
+      <c r="G46">
+        <v>2.455</v>
+      </c>
+      <c r="H46">
+        <v>1899</v>
+      </c>
+      <c r="I46">
+        <v>59.4</v>
+      </c>
+      <c r="J46">
+        <v>164.8</v>
+      </c>
+      <c r="K46">
+        <v>5012.666667</v>
+      </c>
+      <c r="L46">
+        <v>3376</v>
+      </c>
+      <c r="M46">
+        <v>2920</v>
+      </c>
+      <c r="N46">
+        <v>234</v>
+      </c>
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="P46">
+        <v>0.2</v>
+      </c>
+      <c r="Q46">
+        <v>1320</v>
+      </c>
+      <c r="R46">
+        <v>1579.5</v>
+      </c>
+      <c r="S46">
+        <v>1736.25</v>
+      </c>
+      <c r="T46">
+        <v>8500</v>
+      </c>
+      <c r="U46">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="V46">
+        <v>3433.166667</v>
+      </c>
+      <c r="W46">
+        <v>1085</v>
+      </c>
+      <c r="X46">
+        <v>66</v>
+      </c>
+      <c r="Y46">
+        <v>3</v>
+      </c>
+      <c r="Z46">
+        <v>6</v>
+      </c>
+      <c r="AA46">
+        <v>2</v>
+      </c>
+      <c r="AB46">
+        <v>45</v>
+      </c>
+      <c r="AC46" t="s">
         <v>124</v>
       </c>
-      <c r="C44">
-        <v>7410.8333</v>
-      </c>
-      <c r="D44">
-        <v>37.35</v>
-      </c>
-      <c r="F44">
-        <v>20114</v>
-      </c>
-      <c r="G44">
-        <v>1.455</v>
-      </c>
-      <c r="H44">
-        <v>330</v>
-      </c>
-      <c r="I44">
-        <v>34.5</v>
-      </c>
-      <c r="J44">
-        <v>84</v>
-      </c>
-      <c r="K44">
-        <v>2555</v>
-      </c>
-      <c r="L44">
-        <v>2008</v>
-      </c>
-      <c r="M44">
-        <v>2008</v>
-      </c>
-      <c r="N44">
-        <v>159.5</v>
-      </c>
-      <c r="O44">
-        <v>1</v>
-      </c>
-      <c r="P44">
-        <v>0.42</v>
-      </c>
-      <c r="Q44">
-        <v>906</v>
-      </c>
-      <c r="R44">
-        <v>364.3333333</v>
-      </c>
-      <c r="S44">
-        <v>300</v>
-      </c>
-      <c r="V44">
-        <v>2190.666667</v>
-      </c>
-      <c r="W44">
-        <v>18</v>
-      </c>
-      <c r="X44">
-        <v>43</v>
-      </c>
-      <c r="Y44">
-        <v>3</v>
-      </c>
-      <c r="Z44">
-        <v>4</v>
-      </c>
-      <c r="AA44">
-        <v>1</v>
-      </c>
-      <c r="AB44">
-        <v>3.5</v>
-      </c>
-      <c r="AC44" t="s">
-        <v>125</v>
-      </c>
-      <c r="AD44">
-        <v>734.99</v>
-      </c>
-      <c r="AF44">
-        <v>2</v>
-      </c>
-      <c r="AI44">
-        <v>1</v>
-      </c>
-      <c r="AO44">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:41">
-      <c r="B45" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45">
-        <v>2640.285</v>
-      </c>
-      <c r="D45">
-        <v>44.8875</v>
-      </c>
-      <c r="F45">
-        <v>22127</v>
-      </c>
-      <c r="G45">
-        <v>1.25</v>
-      </c>
-      <c r="H45">
-        <v>392</v>
-      </c>
-      <c r="I45">
-        <v>24.25</v>
-      </c>
-      <c r="J45">
-        <v>35.5</v>
-      </c>
-      <c r="K45">
-        <v>1079.791667</v>
-      </c>
-      <c r="L45">
-        <v>882</v>
-      </c>
-      <c r="N45">
-        <v>164.5</v>
-      </c>
-      <c r="O45">
-        <v>1</v>
-      </c>
-      <c r="P45">
-        <v>1</v>
-      </c>
-      <c r="Q45">
-        <v>756</v>
-      </c>
-      <c r="R45">
-        <v>244</v>
-      </c>
-      <c r="S45">
-        <v>119.3333333</v>
-      </c>
-      <c r="T45">
-        <v>1535</v>
-      </c>
-      <c r="U45">
-        <v>2.04</v>
-      </c>
-      <c r="V45">
-        <v>835.7916667</v>
-      </c>
-      <c r="W45">
-        <v>11</v>
-      </c>
-      <c r="X45">
+      <c r="AD46">
+        <v>796.09</v>
+      </c>
+      <c r="AE46">
         <v>0</v>
       </c>
-      <c r="Y45">
-        <v>1</v>
-      </c>
-      <c r="Z45">
-        <v>6</v>
-      </c>
-      <c r="AA45">
-        <v>2</v>
-      </c>
-      <c r="AB45">
-        <v>1</v>
-      </c>
-      <c r="AC45" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD45">
-        <v>400</v>
-      </c>
-      <c r="AF45">
-        <v>2</v>
-      </c>
-      <c r="AG45">
-        <v>1393.9</v>
-      </c>
-      <c r="AI45">
-        <v>2</v>
-      </c>
-      <c r="AO45">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:41">
-      <c r="B46" t="s">
-        <v>127</v>
-      </c>
-      <c r="C46">
-        <v>1933.8</v>
-      </c>
-      <c r="D46">
-        <v>28.1</v>
-      </c>
-      <c r="E46">
-        <v>10.69</v>
-      </c>
-      <c r="F46">
-        <v>12207</v>
-      </c>
-      <c r="G46">
-        <v>1.46</v>
-      </c>
-      <c r="H46">
-        <v>194</v>
-      </c>
-      <c r="I46">
-        <v>36</v>
-      </c>
-      <c r="J46">
-        <v>29.875</v>
-      </c>
-      <c r="K46">
-        <v>908.6979167</v>
-      </c>
-      <c r="L46">
-        <v>548</v>
-      </c>
-      <c r="M46">
-        <v>548</v>
-      </c>
-      <c r="N46">
-        <v>120</v>
-      </c>
-      <c r="O46">
-        <v>1</v>
-      </c>
-      <c r="Q46">
-        <v>730</v>
-      </c>
-      <c r="R46">
-        <v>159</v>
-      </c>
-      <c r="S46">
-        <v>75.7</v>
-      </c>
-      <c r="T46">
-        <v>1350</v>
-      </c>
-      <c r="U46">
-        <v>1.46</v>
-      </c>
-      <c r="V46">
-        <v>749.6979167</v>
-      </c>
-      <c r="W46">
-        <v>8.75</v>
-      </c>
-      <c r="Y46">
-        <v>2</v>
-      </c>
-      <c r="Z46">
-        <v>4</v>
-      </c>
-      <c r="AA46">
-        <v>2</v>
-      </c>
-      <c r="AB46">
-        <v>9.25</v>
-      </c>
-      <c r="AC46" t="s">
-        <v>128</v>
-      </c>
-      <c r="AD46">
-        <v>469.62</v>
-      </c>
       <c r="AF46">
         <v>2</v>
       </c>
+      <c r="AG46">
+        <v>9000</v>
+      </c>
       <c r="AI46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ46">
         <v>3</v>
       </c>
+      <c r="AK46">
+        <v>0.59</v>
+      </c>
+      <c r="AL46">
+        <v>208930</v>
+      </c>
+      <c r="AM46">
+        <v>123027</v>
+      </c>
       <c r="AO46">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:41">
       <c r="B47" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C47">
         <v>1632.75</v>
@@ -5301,7 +5361,7 @@
         <v>4</v>
       </c>
       <c r="AC47" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AD47">
         <v>354.85</v>
@@ -5330,7 +5390,7 @@
     </row>
     <row r="48" spans="1:41">
       <c r="B48" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C48">
         <v>2264.25</v>
@@ -5405,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="AC48" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="AD48">
         <v>425</v>
@@ -5437,168 +5497,141 @@
     </row>
     <row r="49" spans="1:41">
       <c r="B49" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C49">
-        <v>3344.857</v>
+        <v>1008.4285</v>
       </c>
       <c r="D49">
-        <v>49.825</v>
-      </c>
-      <c r="E49">
-        <v>10.59</v>
+        <v>13.54</v>
       </c>
       <c r="F49">
-        <v>15293</v>
+        <v>6683</v>
       </c>
       <c r="G49">
-        <v>1.315</v>
+        <v>1.265</v>
       </c>
       <c r="H49">
-        <v>299</v>
+        <v>127</v>
       </c>
       <c r="I49">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J49">
-        <v>23.3</v>
+        <v>24.55</v>
       </c>
       <c r="K49">
-        <v>708.7083333</v>
+        <v>746.7291667</v>
       </c>
       <c r="L49">
-        <v>604</v>
+        <v>547</v>
       </c>
       <c r="M49">
-        <v>608</v>
+        <v>547</v>
       </c>
       <c r="N49">
-        <v>119.5</v>
+        <v>186</v>
       </c>
       <c r="O49">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="P49">
         <v>1</v>
       </c>
       <c r="Q49">
-        <v>365</v>
+        <v>304</v>
       </c>
       <c r="R49">
-        <v>109.25</v>
+        <v>142.25</v>
       </c>
       <c r="S49">
-        <v>88.2</v>
-      </c>
-      <c r="T49">
-        <v>2696.5</v>
+        <v>40.55</v>
+      </c>
+      <c r="U49">
+        <v>1.09</v>
       </c>
       <c r="V49">
-        <v>599.4583333</v>
+        <v>604.4791667</v>
       </c>
       <c r="W49">
-        <v>25.8</v>
+        <v>12</v>
       </c>
       <c r="X49">
-        <v>73.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="Y49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z49">
         <v>4</v>
       </c>
       <c r="AA49">
-        <v>1</v>
-      </c>
-      <c r="AB49">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="AD49">
-        <v>547.35</v>
+        <v>320</v>
       </c>
       <c r="AF49">
         <v>2</v>
       </c>
       <c r="AG49">
-        <v>603.6</v>
+        <v>347.82</v>
       </c>
       <c r="AI49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO49">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:41">
       <c r="B50" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C50">
-        <v>821.8933</v>
+        <v>7854.833333</v>
       </c>
       <c r="D50">
-        <v>7.5</v>
+        <v>76.75</v>
       </c>
       <c r="F50">
-        <v>3282</v>
+        <v>50906</v>
       </c>
       <c r="G50">
-        <v>1.135</v>
+        <v>1.805</v>
       </c>
       <c r="H50">
-        <v>76.5</v>
+        <v>455</v>
       </c>
       <c r="J50">
-        <v>19.5</v>
+        <v>45.45</v>
       </c>
       <c r="K50">
-        <v>593.125</v>
-      </c>
-      <c r="L50">
-        <v>595</v>
-      </c>
-      <c r="N50">
-        <v>163</v>
-      </c>
-      <c r="O50">
-        <v>1</v>
-      </c>
-      <c r="P50">
-        <v>1</v>
-      </c>
-      <c r="Q50">
-        <v>365</v>
+        <v>1382.4375</v>
       </c>
       <c r="R50">
-        <v>121</v>
-      </c>
-      <c r="S50">
-        <v>27</v>
-      </c>
-      <c r="T50">
-        <v>250</v>
+        <v>656.2</v>
       </c>
       <c r="V50">
-        <v>472.125</v>
+        <v>726.2375</v>
+      </c>
+      <c r="W50">
+        <v>71</v>
+      </c>
+      <c r="X50">
+        <v>26</v>
       </c>
       <c r="Y50">
-        <v>1</v>
-      </c>
-      <c r="Z50">
-        <v>2</v>
-      </c>
-      <c r="AA50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC50" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="AF50">
         <v>2</v>
@@ -5607,45 +5640,45 @@
         <v>1</v>
       </c>
       <c r="AO50">
-        <v>49</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:41">
       <c r="B51" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C51">
-        <v>1008.4285</v>
+        <v>3547.125</v>
       </c>
       <c r="D51">
-        <v>13.54</v>
+        <v>26.9</v>
       </c>
       <c r="F51">
-        <v>6683</v>
+        <v>13170</v>
       </c>
       <c r="G51">
-        <v>1.265</v>
+        <v>1.345</v>
       </c>
       <c r="H51">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="I51">
-        <v>26</v>
+        <v>20.6</v>
       </c>
       <c r="J51">
-        <v>24.55</v>
+        <v>43.46666667</v>
       </c>
       <c r="K51">
-        <v>746.7291667</v>
+        <v>1322.111111</v>
       </c>
       <c r="L51">
-        <v>547</v>
+        <v>912</v>
       </c>
       <c r="M51">
-        <v>547</v>
+        <v>912</v>
       </c>
       <c r="N51">
-        <v>186</v>
+        <v>146.75</v>
       </c>
       <c r="O51">
         <v>1</v>
@@ -5654,471 +5687,426 @@
         <v>1</v>
       </c>
       <c r="Q51">
-        <v>304</v>
+        <v>448.5</v>
       </c>
       <c r="R51">
-        <v>142.25</v>
+        <v>173.25</v>
       </c>
       <c r="S51">
-        <v>40.55</v>
+        <v>94.15000000000001</v>
+      </c>
+      <c r="T51">
+        <v>1000</v>
       </c>
       <c r="U51">
-        <v>1.09</v>
+        <v>2.62</v>
       </c>
       <c r="V51">
-        <v>604.4791667</v>
+        <v>1148.861111</v>
       </c>
       <c r="W51">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="X51">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="Y51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA51">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AB51">
+        <v>7.5</v>
       </c>
       <c r="AC51" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD51">
+        <v>472.49</v>
+      </c>
+      <c r="AF51">
+        <v>2</v>
+      </c>
+      <c r="AG51">
+        <v>670</v>
+      </c>
+      <c r="AI51">
+        <v>1</v>
+      </c>
+      <c r="AJ51">
+        <v>3</v>
+      </c>
+      <c r="AO51">
         <v>42</v>
-      </c>
-      <c r="AD51">
-        <v>320</v>
-      </c>
-      <c r="AF51">
-        <v>2</v>
-      </c>
-      <c r="AG51">
-        <v>347.82</v>
-      </c>
-      <c r="AI51">
-        <v>1</v>
-      </c>
-      <c r="AJ51">
-        <v>1</v>
-      </c>
-      <c r="AO51">
-        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:41">
       <c r="B52" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C52">
-        <v>281.44</v>
+        <v>8481.666667</v>
       </c>
       <c r="D52">
-        <v>6.633333333</v>
-      </c>
-      <c r="E52">
-        <v>2.69</v>
+        <v>84.83333333</v>
       </c>
       <c r="F52">
-        <v>3524</v>
+        <v>48763</v>
       </c>
       <c r="G52">
-        <v>1.285</v>
+        <v>1.635</v>
       </c>
       <c r="H52">
-        <v>51.6</v>
+        <v>911</v>
       </c>
       <c r="I52">
-        <v>16.4</v>
+        <v>30</v>
       </c>
       <c r="J52">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K52">
-        <v>547.5</v>
+        <v>1460</v>
       </c>
       <c r="L52">
-        <v>380</v>
-      </c>
-      <c r="M52">
+        <v>1460</v>
+      </c>
+      <c r="N52">
+        <v>190.5</v>
+      </c>
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52">
+        <v>1</v>
+      </c>
+      <c r="Q52">
         <v>365</v>
       </c>
-      <c r="N52">
-        <v>165.75</v>
-      </c>
-      <c r="O52">
-        <v>1.45</v>
-      </c>
-      <c r="P52">
-        <v>1.5</v>
-      </c>
-      <c r="Q52">
-        <v>234</v>
-      </c>
       <c r="R52">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="S52">
-        <v>11.175</v>
-      </c>
-      <c r="T52">
-        <v>139</v>
-      </c>
-      <c r="U52">
-        <v>0.58</v>
+        <v>428.25</v>
       </c>
       <c r="V52">
-        <v>387.5</v>
-      </c>
-      <c r="W52">
-        <v>1</v>
-      </c>
-      <c r="X52">
-        <v>15</v>
+        <v>1130</v>
       </c>
       <c r="Y52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA52">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AB52">
+        <v>9.300000000000001</v>
       </c>
       <c r="AC52" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="AD52">
-        <v>224.49</v>
+        <v>326.37</v>
       </c>
       <c r="AF52">
         <v>2</v>
       </c>
-      <c r="AG52">
-        <v>147.5</v>
-      </c>
       <c r="AI52">
         <v>1</v>
       </c>
-      <c r="AJ52">
-        <v>4</v>
-      </c>
       <c r="AO52">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:41">
       <c r="B53" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C53">
-        <v>828.1875</v>
+        <v>439.2</v>
       </c>
       <c r="D53">
-        <v>11.73333333</v>
-      </c>
-      <c r="E53">
+        <v>10.5</v>
+      </c>
+      <c r="F53">
+        <v>5883</v>
+      </c>
+      <c r="G53">
+        <v>1.195</v>
+      </c>
+      <c r="H53">
+        <v>251</v>
+      </c>
+      <c r="I53">
+        <v>13.3</v>
+      </c>
+      <c r="J53">
+        <v>24</v>
+      </c>
+      <c r="K53">
+        <v>730</v>
+      </c>
+      <c r="L53">
+        <v>608</v>
+      </c>
+      <c r="N53">
+        <v>140.5</v>
+      </c>
+      <c r="O53">
+        <v>2</v>
+      </c>
+      <c r="P53">
+        <v>1.4</v>
+      </c>
+      <c r="Q53">
+        <v>240</v>
+      </c>
+      <c r="R53">
+        <v>70.5</v>
+      </c>
+      <c r="S53">
+        <v>38</v>
+      </c>
+      <c r="V53">
+        <v>659.5</v>
+      </c>
+      <c r="W53">
+        <v>9</v>
+      </c>
+      <c r="X53">
+        <v>69</v>
+      </c>
+      <c r="Y53">
+        <v>3</v>
+      </c>
+      <c r="Z53">
         <v>4</v>
       </c>
-      <c r="F53">
-        <v>6.192</v>
-      </c>
-      <c r="G53">
-        <v>1.205</v>
-      </c>
-      <c r="H53">
-        <v>142</v>
-      </c>
-      <c r="I53">
-        <v>26.5</v>
-      </c>
-      <c r="J53">
-        <v>25.3</v>
-      </c>
-      <c r="K53">
-        <v>769.5416667</v>
-      </c>
-      <c r="L53">
-        <v>578</v>
-      </c>
-      <c r="N53">
-        <v>192</v>
-      </c>
-      <c r="O53">
-        <v>1</v>
-      </c>
-      <c r="P53">
-        <v>1</v>
-      </c>
-      <c r="Q53">
-        <v>428.5</v>
-      </c>
-      <c r="R53">
-        <v>157.25</v>
-      </c>
-      <c r="S53">
-        <v>46.16</v>
-      </c>
-      <c r="T53">
-        <v>520</v>
-      </c>
-      <c r="U53">
-        <v>1.09</v>
-      </c>
-      <c r="V53">
-        <v>612.2916667</v>
-      </c>
-      <c r="W53">
-        <v>5</v>
-      </c>
-      <c r="X53">
-        <v>60</v>
-      </c>
-      <c r="Y53">
-        <v>1</v>
-      </c>
-      <c r="Z53">
-        <v>6</v>
-      </c>
       <c r="AA53">
         <v>2</v>
       </c>
       <c r="AC53" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="AD53">
-        <v>300</v>
+        <v>264.21</v>
       </c>
       <c r="AF53">
         <v>2</v>
       </c>
-      <c r="AG53">
-        <v>240</v>
-      </c>
-      <c r="AI53">
-        <v>1</v>
-      </c>
-      <c r="AJ53">
-        <v>1</v>
-      </c>
-      <c r="AK53">
-        <v>0.49</v>
-      </c>
-      <c r="AL53">
-        <v>109648</v>
-      </c>
-      <c r="AM53">
-        <v>53703</v>
-      </c>
       <c r="AO53">
-        <v>52</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:41">
       <c r="B54" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54">
+        <v>368.8333333</v>
+      </c>
+      <c r="D54">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F54">
+        <v>5894</v>
+      </c>
+      <c r="G54">
+        <v>1.195</v>
+      </c>
+      <c r="I54">
+        <v>23.08</v>
+      </c>
+      <c r="J54">
+        <v>22.8</v>
+      </c>
+      <c r="K54">
+        <v>693.5</v>
+      </c>
+      <c r="L54">
+        <v>548</v>
+      </c>
+      <c r="M54">
+        <v>550</v>
+      </c>
+      <c r="N54">
+        <v>161.5</v>
+      </c>
+      <c r="O54">
+        <v>1.9</v>
+      </c>
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="Q54">
+        <v>262</v>
+      </c>
+      <c r="R54">
+        <v>52</v>
+      </c>
+      <c r="S54">
+        <v>41.28</v>
+      </c>
+      <c r="T54">
+        <v>105</v>
+      </c>
+      <c r="V54">
+        <v>641.5</v>
+      </c>
+      <c r="W54">
+        <v>32</v>
+      </c>
+      <c r="Y54">
+        <v>3</v>
+      </c>
+      <c r="Z54">
+        <v>4</v>
+      </c>
+      <c r="AA54">
+        <v>2</v>
+      </c>
+      <c r="AC54" t="s">
         <v>139</v>
       </c>
-      <c r="C54">
-        <v>178.7</v>
-      </c>
-      <c r="D54">
-        <v>4.8</v>
-      </c>
-      <c r="E54">
-        <v>2.3</v>
-      </c>
-      <c r="F54">
-        <v>2139</v>
-      </c>
-      <c r="G54">
-        <v>1.17</v>
-      </c>
-      <c r="H54">
-        <v>40.2</v>
-      </c>
-      <c r="I54">
-        <v>17</v>
-      </c>
-      <c r="J54">
-        <v>11.4</v>
-      </c>
-      <c r="K54">
-        <v>346.75</v>
-      </c>
-      <c r="L54">
-        <v>240</v>
-      </c>
-      <c r="M54">
-        <v>300</v>
-      </c>
-      <c r="N54">
-        <v>130.6666667</v>
-      </c>
-      <c r="O54">
-        <v>1.55</v>
-      </c>
-      <c r="P54">
-        <v>2</v>
-      </c>
-      <c r="Q54">
-        <v>242.5</v>
-      </c>
-      <c r="R54">
-        <v>87.33333333</v>
-      </c>
-      <c r="S54">
-        <v>15.55</v>
-      </c>
-      <c r="T54">
-        <v>125</v>
-      </c>
-      <c r="U54">
-        <v>0.74</v>
-      </c>
-      <c r="V54">
-        <v>259.4166667</v>
-      </c>
-      <c r="W54">
-        <v>11</v>
-      </c>
-      <c r="X54">
-        <v>0</v>
-      </c>
-      <c r="Y54">
-        <v>1</v>
-      </c>
-      <c r="Z54">
-        <v>3</v>
-      </c>
-      <c r="AA54">
-        <v>2</v>
-      </c>
-      <c r="AC54" t="s">
-        <v>140</v>
-      </c>
       <c r="AD54">
-        <v>160</v>
+        <v>239.99</v>
       </c>
       <c r="AF54">
         <v>2</v>
       </c>
-      <c r="AG54">
-        <v>180.225</v>
+      <c r="AI54">
+        <v>1</v>
       </c>
       <c r="AJ54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK54">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AL54">
-        <v>338844</v>
+        <v>328541</v>
       </c>
       <c r="AM54">
-        <v>151356</v>
+        <v>102329</v>
       </c>
       <c r="AO54">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:41">
       <c r="A55" t="s">
+        <v>140</v>
+      </c>
+      <c r="B55" t="s">
         <v>141</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55">
+        <v>680.6</v>
+      </c>
+      <c r="D55">
+        <v>22.98</v>
+      </c>
+      <c r="E55">
+        <v>15.24</v>
+      </c>
+      <c r="F55">
+        <v>15541</v>
+      </c>
+      <c r="G55">
+        <v>1.55</v>
+      </c>
+      <c r="H55">
+        <v>299</v>
+      </c>
+      <c r="I55">
+        <v>27</v>
+      </c>
+      <c r="J55">
+        <v>30</v>
+      </c>
+      <c r="K55">
+        <v>912.5</v>
+      </c>
+      <c r="L55">
+        <v>1003</v>
+      </c>
+      <c r="M55">
+        <v>1826</v>
+      </c>
+      <c r="N55">
+        <v>168</v>
+      </c>
+      <c r="O55">
+        <v>1</v>
+      </c>
+      <c r="P55">
+        <v>1</v>
+      </c>
+      <c r="Q55">
+        <v>351</v>
+      </c>
+      <c r="R55">
+        <v>176</v>
+      </c>
+      <c r="S55">
+        <v>138.6</v>
+      </c>
+      <c r="T55">
+        <v>410.5</v>
+      </c>
+      <c r="V55">
+        <v>736.5</v>
+      </c>
+      <c r="W55">
+        <v>157</v>
+      </c>
+      <c r="X55">
+        <v>28</v>
+      </c>
+      <c r="Y55">
+        <v>3</v>
+      </c>
+      <c r="Z55">
+        <v>3</v>
+      </c>
+      <c r="AA55">
+        <v>2</v>
+      </c>
+      <c r="AC55" t="s">
         <v>142</v>
       </c>
-      <c r="C55">
-        <v>952.428</v>
-      </c>
-      <c r="D55">
-        <v>10.6</v>
-      </c>
-      <c r="E55">
-        <v>4</v>
-      </c>
-      <c r="F55">
-        <v>4723</v>
-      </c>
-      <c r="G55">
-        <v>1.255</v>
-      </c>
-      <c r="H55">
-        <v>147</v>
-      </c>
-      <c r="I55">
-        <v>15.66</v>
-      </c>
-      <c r="J55">
-        <v>23</v>
-      </c>
-      <c r="K55">
-        <v>699.5833333</v>
-      </c>
-      <c r="L55">
-        <v>430</v>
-      </c>
-      <c r="M55">
-        <v>639</v>
-      </c>
-      <c r="N55">
-        <v>134</v>
-      </c>
-      <c r="O55">
-        <v>1.533333333</v>
-      </c>
-      <c r="P55">
-        <v>1</v>
-      </c>
-      <c r="Q55">
-        <v>281.3333333</v>
-      </c>
-      <c r="R55">
-        <v>121</v>
-      </c>
-      <c r="S55">
-        <v>43.96</v>
-      </c>
-      <c r="T55">
-        <v>500</v>
-      </c>
-      <c r="U55">
-        <v>1.47</v>
-      </c>
-      <c r="V55">
-        <v>578.5833333</v>
-      </c>
-      <c r="W55">
-        <v>10</v>
-      </c>
-      <c r="X55">
-        <v>27</v>
-      </c>
-      <c r="Y55">
-        <v>1</v>
-      </c>
-      <c r="Z55">
-        <v>5</v>
-      </c>
-      <c r="AA55">
-        <v>2</v>
-      </c>
-      <c r="AC55" t="s">
-        <v>140</v>
-      </c>
       <c r="AD55">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="AF55">
         <v>2</v>
       </c>
       <c r="AG55">
-        <v>457.15</v>
+        <v>738.8099999999999</v>
+      </c>
+      <c r="AI55">
+        <v>1</v>
       </c>
       <c r="AJ55">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AK55">
+        <v>0.25</v>
+      </c>
+      <c r="AL55">
+        <v>478630</v>
+      </c>
+      <c r="AM55">
+        <v>117490</v>
       </c>
       <c r="AO55">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:41">
@@ -6126,88 +6114,100 @@
         <v>143</v>
       </c>
       <c r="C56">
-        <v>71.5</v>
+        <v>3344.857</v>
       </c>
       <c r="D56">
-        <v>3.345</v>
+        <v>49.825</v>
       </c>
       <c r="E56">
-        <v>1.199</v>
+        <v>10.59</v>
       </c>
       <c r="F56">
-        <v>1568</v>
+        <v>15293</v>
       </c>
       <c r="G56">
-        <v>1.21</v>
+        <v>1.315</v>
       </c>
       <c r="H56">
-        <v>30.4</v>
+        <v>299</v>
       </c>
       <c r="I56">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J56">
-        <v>21.4</v>
+        <v>23.3</v>
       </c>
       <c r="K56">
-        <v>650.9166667</v>
+        <v>708.7083333</v>
       </c>
       <c r="L56">
-        <v>240</v>
+        <v>604</v>
       </c>
       <c r="M56">
-        <v>274</v>
+        <v>608</v>
       </c>
       <c r="N56">
-        <v>110.3333333</v>
+        <v>119.5</v>
       </c>
       <c r="O56">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="P56">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Q56">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="R56">
-        <v>45</v>
+        <v>109.25</v>
       </c>
       <c r="S56">
-        <v>8.466666667</v>
+        <v>88.2</v>
+      </c>
+      <c r="T56">
+        <v>2696.5</v>
       </c>
       <c r="V56">
-        <v>605.9166667</v>
+        <v>599.4583333</v>
       </c>
       <c r="W56">
-        <v>1</v>
+        <v>25.8</v>
+      </c>
+      <c r="X56">
+        <v>73.90000000000001</v>
       </c>
       <c r="Y56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z56">
         <v>4</v>
       </c>
       <c r="AA56">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AB56">
+        <v>3.5</v>
       </c>
       <c r="AC56" t="s">
         <v>144</v>
       </c>
       <c r="AD56">
-        <v>120</v>
+        <v>547.35</v>
       </c>
       <c r="AF56">
         <v>2</v>
       </c>
       <c r="AG56">
-        <v>59.4</v>
+        <v>603.6</v>
+      </c>
+      <c r="AI56">
+        <v>2</v>
       </c>
       <c r="AJ56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO56">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:41">
@@ -7930,7 +7930,7 @@
         <v>3</v>
       </c>
       <c r="AC79" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="AD79">
         <v>627.12</v>
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8032E005-F206-457F-860F-7DC38D86DB61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBF9D5D-A583-4B0E-A6B6-E5E082954567}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D1DDCA3-8E80-4246-A5D1-E3CC21C4E6C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60822B07-289D-4ADE-B2CF-621276132817}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0321E8E-4DF4-4664-A2B0-419251617260}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E908E0F-76A2-4732-8ECD-150F0FAF7C58}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBF9D5D-A583-4B0E-A6B6-E5E082954567}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB3179D-2B79-4BE1-89B1-0CA7A7E2D25E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60822B07-289D-4ADE-B2CF-621276132817}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{121983D9-C6ED-415C-95B3-74CB72B1B6D2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E908E0F-76A2-4732-8ECD-150F0FAF7C58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7F951EB-845D-42C4-8A5A-5EEA0CBBE7A7}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB3179D-2B79-4BE1-89B1-0CA7A7E2D25E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62031A4D-B4D1-4ADE-8E1B-81915BE0CD5C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{121983D9-C6ED-415C-95B3-74CB72B1B6D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E591B22A-8CB0-441C-88EE-3D3F8507B9DA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7F951EB-845D-42C4-8A5A-5EEA0CBBE7A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAA8F008-EB30-4E2B-A8D9-3CEE323BF20B}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -10048,13 +10048,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62031A4D-B4D1-4ADE-8E1B-81915BE0CD5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3604F2D-05C3-47AF-82BD-46CB40D68196}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E591B22A-8CB0-441C-88EE-3D3F8507B9DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD53B1F7-7D73-4CFA-89C8-44FCA6128B18}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAA8F008-EB30-4E2B-A8D9-3CEE323BF20B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{299E8401-8975-469D-8133-CC3297C20B5B}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,291 +9770,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3604F2D-05C3-47AF-82BD-46CB40D68196}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD53B1F7-7D73-4CFA-89C8-44FCA6128B18}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{299E8401-8975-469D-8133-CC3297C20B5B}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,4 +9770,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93900AAF-22A4-4443-851C-38C8E16A714A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7213DB42-84D6-4C7D-A165-33FFD0EB53B7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2FBBD02-8C30-43E0-B09B-A75708A9D452}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,291 +9770,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93900AAF-22A4-4443-851C-38C8E16A714A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7213DB42-84D6-4C7D-A165-33FFD0EB53B7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2FBBD02-8C30-43E0-B09B-A75708A9D452}"/>
 </file>
--- a/____EvoM1_TraitTable/glia_gyrification.xlsx
+++ b/____EvoM1_TraitTable/glia_gyrification.xlsx
@@ -9770,4 +9770,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20BD4B2A-F6FA-49F5-A455-D8EF59D7EEA8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE44DAEA-ADF5-4C18-BF21-F89F2BA903C3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AF783E3-1567-4435-9EAC-94937EC60A6B}"/>
 </file>